--- a/data.xlsx
+++ b/data.xlsx
@@ -100,13 +100,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0%"/>
-    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="177" formatCode="0.0%"/>
+    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -871,13 +872,19 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -890,6 +897,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -908,52 +918,55 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1270,2914 +1283,2929 @@
   <dimension ref="A1:AD42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
+    <col min="20" max="20" width="9" style="1"/>
     <col min="22" max="22" width="10.6363636363636"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:30">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1" t="s">
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="S1" s="1"/>
-      <c r="T1" s="2" t="s">
+      <c r="S1" s="2"/>
+      <c r="T1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U1" s="2"/>
-      <c r="V1" s="3" t="s">
+      <c r="U1" s="4"/>
+      <c r="V1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4"/>
-      <c r="AD1" s="5"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6"/>
+      <c r="AD1" s="7"/>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:30">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1" t="s">
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1" t="s">
+      <c r="M2" s="2"/>
+      <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1" t="s">
+      <c r="O2" s="2"/>
+      <c r="P2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1" t="s">
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="1"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="7" t="s">
+      <c r="S2" s="2"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7" t="s">
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="AA2" s="7"/>
-      <c r="AB2" s="7"/>
-      <c r="AC2" s="8" t="s">
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="10"/>
+      <c r="AC2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="AD2" s="9" t="s">
+      <c r="AD2" s="12" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:30">
-      <c r="A3" s="10">
+      <c r="A3" s="13">
         <v>14989</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="14">
         <v>8517</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="15">
         <v>0.568</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="13">
+      <c r="D3" s="16"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="16">
         <v>5600</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="15">
         <v>0.374</v>
       </c>
-      <c r="H3" s="13">
-        <v>0</v>
-      </c>
-      <c r="I3" s="12">
-        <v>0</v>
-      </c>
-      <c r="J3" s="14"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="13">
+      <c r="H3" s="16">
+        <v>0</v>
+      </c>
+      <c r="I3" s="15">
+        <v>0</v>
+      </c>
+      <c r="J3" s="17"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="16">
         <v>478</v>
       </c>
-      <c r="M3" s="12">
+      <c r="M3" s="15">
         <v>0.032</v>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="16">
         <v>394</v>
       </c>
-      <c r="O3" s="12">
+      <c r="O3" s="15">
         <v>0.026</v>
       </c>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="12"/>
-      <c r="T3" s="16"/>
-      <c r="U3" s="16"/>
-      <c r="V3" s="17">
+      <c r="P3" s="18"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="19"/>
+      <c r="U3" s="20"/>
+      <c r="V3" s="21">
         <v>45689</v>
       </c>
-      <c r="W3" s="18"/>
-      <c r="X3" s="19"/>
-      <c r="Y3" s="20"/>
-      <c r="Z3" s="18"/>
-      <c r="AA3" s="19"/>
-      <c r="AB3" s="20"/>
-      <c r="AC3" s="21"/>
-      <c r="AD3" s="22"/>
+      <c r="W3" s="22"/>
+      <c r="X3" s="23"/>
+      <c r="Y3" s="24"/>
+      <c r="Z3" s="22"/>
+      <c r="AA3" s="23"/>
+      <c r="AB3" s="24"/>
+      <c r="AC3" s="25"/>
+      <c r="AD3" s="26"/>
     </row>
     <row r="4" spans="1:30">
-      <c r="A4" s="10">
+      <c r="A4" s="13">
         <v>13626</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="14">
         <v>7119</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="15">
         <v>0.522</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="13">
+      <c r="D4" s="16"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="16">
         <v>5100</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="15">
         <v>0.374</v>
       </c>
-      <c r="H4" s="13">
-        <v>0</v>
-      </c>
-      <c r="I4" s="12">
-        <v>0</v>
-      </c>
-      <c r="J4" s="14"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="13">
+      <c r="H4" s="16">
+        <v>0</v>
+      </c>
+      <c r="I4" s="15">
+        <v>0</v>
+      </c>
+      <c r="J4" s="17"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="16">
         <v>712</v>
       </c>
-      <c r="M4" s="12">
+      <c r="M4" s="15">
         <v>0.052</v>
       </c>
-      <c r="N4" s="13">
+      <c r="N4" s="16">
         <v>695</v>
       </c>
-      <c r="O4" s="12">
+      <c r="O4" s="15">
         <v>0.051</v>
       </c>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="16"/>
-      <c r="U4" s="16"/>
-      <c r="V4" s="17">
+      <c r="P4" s="18"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="21">
         <v>45703</v>
       </c>
-      <c r="W4" s="18"/>
-      <c r="X4" s="19"/>
-      <c r="Y4" s="20"/>
-      <c r="Z4" s="18"/>
-      <c r="AA4" s="19"/>
-      <c r="AB4" s="20"/>
-      <c r="AC4" s="21"/>
-      <c r="AD4" s="22"/>
+      <c r="W4" s="22"/>
+      <c r="X4" s="23"/>
+      <c r="Y4" s="24"/>
+      <c r="Z4" s="22"/>
+      <c r="AA4" s="23"/>
+      <c r="AB4" s="24"/>
+      <c r="AC4" s="25"/>
+      <c r="AD4" s="26"/>
     </row>
     <row r="5" spans="1:30">
-      <c r="A5" s="10">
+      <c r="A5" s="13">
         <v>13147</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="14">
         <v>5749</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="15">
         <v>0.437</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="13">
+      <c r="D5" s="16"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="16">
         <v>5100</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="15">
         <v>0.388</v>
       </c>
-      <c r="H5" s="13">
-        <v>0</v>
-      </c>
-      <c r="I5" s="12">
-        <v>0</v>
-      </c>
-      <c r="J5" s="14"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="13">
+      <c r="H5" s="16">
+        <v>0</v>
+      </c>
+      <c r="I5" s="15">
+        <v>0</v>
+      </c>
+      <c r="J5" s="17"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="16">
         <v>1161</v>
       </c>
-      <c r="M5" s="12">
+      <c r="M5" s="15">
         <v>0.088</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="16">
         <v>1137</v>
       </c>
-      <c r="O5" s="12">
+      <c r="O5" s="15">
         <v>0.086</v>
       </c>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="16"/>
-      <c r="U5" s="16"/>
-      <c r="V5" s="17">
+      <c r="P5" s="18"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="19"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="21">
         <v>45717</v>
       </c>
-      <c r="W5" s="18"/>
-      <c r="X5" s="19"/>
-      <c r="Y5" s="20"/>
-      <c r="Z5" s="18"/>
-      <c r="AA5" s="19"/>
-      <c r="AB5" s="20"/>
-      <c r="AC5" s="21"/>
-      <c r="AD5" s="22"/>
+      <c r="W5" s="22"/>
+      <c r="X5" s="23"/>
+      <c r="Y5" s="24"/>
+      <c r="Z5" s="22"/>
+      <c r="AA5" s="23"/>
+      <c r="AB5" s="24"/>
+      <c r="AC5" s="25"/>
+      <c r="AD5" s="26"/>
     </row>
     <row r="6" spans="1:30">
-      <c r="A6" s="10">
+      <c r="A6" s="13">
         <v>18163</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="14">
         <v>10314</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="15">
         <v>0.568</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="13">
+      <c r="D6" s="16"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16">
         <v>5100</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="15">
         <v>0.281</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="16">
         <v>363</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="15">
         <v>0.02</v>
       </c>
-      <c r="J6" s="14"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="13">
+      <c r="J6" s="17"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="16">
         <v>1337</v>
       </c>
-      <c r="M6" s="12">
+      <c r="M6" s="15">
         <v>0.074</v>
       </c>
-      <c r="N6" s="13">
+      <c r="N6" s="16">
         <v>1049</v>
       </c>
-      <c r="O6" s="12">
+      <c r="O6" s="15">
         <v>0.058</v>
       </c>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-      <c r="V6" s="17">
+      <c r="P6" s="18"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="21">
         <v>45731</v>
       </c>
-      <c r="W6" s="18"/>
-      <c r="X6" s="19"/>
-      <c r="Y6" s="20"/>
-      <c r="Z6" s="18"/>
-      <c r="AA6" s="19"/>
-      <c r="AB6" s="20"/>
-      <c r="AC6" s="21"/>
-      <c r="AD6" s="22"/>
+      <c r="W6" s="22"/>
+      <c r="X6" s="23"/>
+      <c r="Y6" s="24"/>
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="23"/>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="26"/>
     </row>
     <row r="7" spans="1:30">
-      <c r="A7" s="10">
+      <c r="A7" s="13">
         <v>18796</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="14">
         <v>10294</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="15">
         <v>0.547669716961056</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="13">
+      <c r="D7" s="16"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="16">
         <v>5100</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="15">
         <v>0.271334326452437</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="16">
         <v>362</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="15">
         <v>0.0192594168972122</v>
       </c>
-      <c r="J7" s="14"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="13">
+      <c r="J7" s="17"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="16">
         <v>1517</v>
       </c>
-      <c r="M7" s="12">
+      <c r="M7" s="15">
         <v>0.0807086614173228</v>
       </c>
-      <c r="N7" s="13">
+      <c r="N7" s="16">
         <v>1523</v>
       </c>
-      <c r="O7" s="12">
+      <c r="O7" s="15">
         <v>0.0810278782719728</v>
       </c>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="16"/>
-      <c r="V7" s="17">
+      <c r="P7" s="18"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="19"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="21">
         <v>45748</v>
       </c>
-      <c r="W7" s="18"/>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="20"/>
-      <c r="Z7" s="18"/>
-      <c r="AA7" s="19"/>
-      <c r="AB7" s="20"/>
-      <c r="AC7" s="21"/>
-      <c r="AD7" s="22"/>
+      <c r="W7" s="22"/>
+      <c r="X7" s="23"/>
+      <c r="Y7" s="24"/>
+      <c r="Z7" s="22"/>
+      <c r="AA7" s="23"/>
+      <c r="AB7" s="24"/>
+      <c r="AC7" s="25"/>
+      <c r="AD7" s="26"/>
     </row>
     <row r="8" spans="1:30">
-      <c r="A8" s="10">
+      <c r="A8" s="13">
         <v>20942</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="14">
         <v>13642</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="15">
         <v>0.651418202654952</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="13">
+      <c r="D8" s="16"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16">
         <v>3600</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="15">
         <v>0.171903352115366</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="16">
         <v>362</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="15">
         <v>0.0172858370738229</v>
       </c>
-      <c r="J8" s="14"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="13">
+      <c r="J8" s="17"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16">
         <v>1703</v>
       </c>
-      <c r="M8" s="12">
+      <c r="M8" s="15">
         <v>0.0813198357367969</v>
       </c>
-      <c r="N8" s="13">
+      <c r="N8" s="16">
         <v>1635</v>
       </c>
-      <c r="O8" s="12">
+      <c r="O8" s="15">
         <v>0.0780727724190622</v>
       </c>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="14"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="16"/>
-      <c r="V8" s="17">
+      <c r="P8" s="18"/>
+      <c r="Q8" s="15"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="15"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="21">
         <v>45762</v>
       </c>
-      <c r="W8" s="18"/>
-      <c r="X8" s="19"/>
-      <c r="Y8" s="20"/>
-      <c r="Z8" s="18"/>
-      <c r="AA8" s="19"/>
-      <c r="AB8" s="20"/>
-      <c r="AC8" s="21"/>
-      <c r="AD8" s="22"/>
+      <c r="W8" s="22"/>
+      <c r="X8" s="23"/>
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="22"/>
+      <c r="AA8" s="23"/>
+      <c r="AB8" s="24"/>
+      <c r="AC8" s="25"/>
+      <c r="AD8" s="26"/>
     </row>
     <row r="9" spans="1:30">
-      <c r="A9" s="10">
+      <c r="A9" s="13">
         <v>13932</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="14">
         <v>4661</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="15">
         <v>0.334553545793856</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="13">
+      <c r="D9" s="16"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16">
         <v>3600</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="15">
         <v>0.258397932816537</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="16">
         <v>364</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="15">
         <v>0.0261269020958943</v>
       </c>
-      <c r="J9" s="14"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="13">
+      <c r="J9" s="17"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="16">
         <v>2066</v>
       </c>
-      <c r="M9" s="12">
+      <c r="M9" s="15">
         <v>0.148291702555268</v>
       </c>
-      <c r="N9" s="13">
+      <c r="N9" s="16">
         <v>3241</v>
       </c>
-      <c r="O9" s="12">
+      <c r="O9" s="15">
         <v>0.232629916738444</v>
       </c>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-      <c r="V9" s="17">
+      <c r="P9" s="18"/>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="21">
         <v>45778</v>
       </c>
-      <c r="W9" s="18"/>
-      <c r="X9" s="19"/>
-      <c r="Y9" s="20"/>
-      <c r="Z9" s="18"/>
-      <c r="AA9" s="19"/>
-      <c r="AB9" s="20"/>
-      <c r="AC9" s="21"/>
-      <c r="AD9" s="22"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="23"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="22"/>
+      <c r="AA9" s="23"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="25"/>
+      <c r="AD9" s="26"/>
     </row>
     <row r="10" spans="1:30">
-      <c r="A10" s="10">
+      <c r="A10" s="13">
         <v>12586</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="14">
         <v>2708</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="15">
         <v>0.215159701255363</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="13">
+      <c r="D10" s="16"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="16">
         <v>3600</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="15">
         <v>0.286032099157794</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="16">
         <v>359</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="15">
         <v>0.0285237565549023</v>
       </c>
-      <c r="J10" s="14"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="13">
+      <c r="J10" s="17"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="16">
         <v>1805</v>
       </c>
-      <c r="M10" s="12">
+      <c r="M10" s="15">
         <v>0.143413316383283</v>
       </c>
-      <c r="N10" s="13">
+      <c r="N10" s="16">
         <v>4114</v>
       </c>
-      <c r="O10" s="12">
+      <c r="O10" s="15">
         <v>0.326871126648657</v>
       </c>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="16"/>
-      <c r="V10" s="17">
+      <c r="P10" s="18"/>
+      <c r="Q10" s="15"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="21">
         <v>45792</v>
       </c>
-      <c r="W10" s="18"/>
-      <c r="X10" s="19"/>
-      <c r="Y10" s="20"/>
-      <c r="Z10" s="18"/>
-      <c r="AA10" s="19"/>
-      <c r="AB10" s="20"/>
-      <c r="AC10" s="21"/>
-      <c r="AD10" s="22"/>
+      <c r="W10" s="22"/>
+      <c r="X10" s="23"/>
+      <c r="Y10" s="24"/>
+      <c r="Z10" s="22"/>
+      <c r="AA10" s="23"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="25"/>
+      <c r="AD10" s="26"/>
     </row>
     <row r="11" spans="1:30">
-      <c r="A11" s="10">
+      <c r="A11" s="13">
         <v>15784</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="14">
         <v>6421</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="15">
         <v>0.406804358844399</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="13">
+      <c r="D11" s="16"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="16">
         <v>3600</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="15">
         <v>0.228079067410035</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="16">
         <v>359</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="15">
         <v>0.0227445514445008</v>
       </c>
-      <c r="J11" s="14"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="13">
+      <c r="J11" s="17"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="16">
         <v>1986</v>
       </c>
-      <c r="M11" s="12">
+      <c r="M11" s="15">
         <v>0.125823618854536</v>
       </c>
-      <c r="N11" s="13">
+      <c r="N11" s="16">
         <v>3418</v>
       </c>
-      <c r="O11" s="12">
+      <c r="O11" s="15">
         <v>0.216548403446528</v>
       </c>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="14"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="16"/>
-      <c r="U11" s="16"/>
-      <c r="V11" s="17">
+      <c r="P11" s="18"/>
+      <c r="Q11" s="15"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="15"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="21">
         <v>45809</v>
       </c>
-      <c r="W11" s="18"/>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="20"/>
-      <c r="Z11" s="18"/>
-      <c r="AA11" s="19"/>
-      <c r="AB11" s="20"/>
-      <c r="AC11" s="21"/>
-      <c r="AD11" s="22"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="23"/>
+      <c r="Y11" s="24"/>
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="23"/>
+      <c r="AB11" s="24"/>
+      <c r="AC11" s="25"/>
+      <c r="AD11" s="26"/>
     </row>
     <row r="12" spans="1:30">
-      <c r="A12" s="10">
+      <c r="A12" s="13">
         <v>16227</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="14">
         <v>7986</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="15">
         <v>0.492142725087817</v>
       </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="13">
+      <c r="D12" s="16"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="16">
         <v>2300</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="15">
         <v>0.14173907684723</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="16">
         <v>358</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="15">
         <v>0.0220619954396993</v>
       </c>
-      <c r="J12" s="14"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="13">
+      <c r="J12" s="17"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="16">
         <v>2168</v>
       </c>
-      <c r="M12" s="12">
+      <c r="M12" s="15">
         <v>0.133604486349911</v>
       </c>
-      <c r="N12" s="13">
+      <c r="N12" s="16">
         <v>3415</v>
       </c>
-      <c r="O12" s="12">
+      <c r="O12" s="15">
         <v>0.210451716275344</v>
       </c>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="16"/>
-      <c r="V12" s="17">
+      <c r="P12" s="18"/>
+      <c r="Q12" s="15"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="15"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="21">
         <v>45823</v>
       </c>
-      <c r="W12" s="18"/>
-      <c r="X12" s="19"/>
-      <c r="Y12" s="20"/>
-      <c r="Z12" s="18"/>
-      <c r="AA12" s="19"/>
-      <c r="AB12" s="20"/>
-      <c r="AC12" s="21"/>
-      <c r="AD12" s="22"/>
+      <c r="W12" s="22"/>
+      <c r="X12" s="23"/>
+      <c r="Y12" s="24"/>
+      <c r="Z12" s="22"/>
+      <c r="AA12" s="23"/>
+      <c r="AB12" s="24"/>
+      <c r="AC12" s="25"/>
+      <c r="AD12" s="26"/>
     </row>
     <row r="13" spans="1:30">
-      <c r="A13" s="10">
+      <c r="A13" s="13">
         <v>19095</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="14">
         <v>9574</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="15">
         <v>0.501387797852841</v>
       </c>
-      <c r="D13" s="13"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="13">
+      <c r="D13" s="16"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="16">
         <v>2100</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="15">
         <v>0.109976433621367</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="16">
         <v>357</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="15">
         <v>0.0186959937156324</v>
       </c>
-      <c r="J13" s="14"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="13">
+      <c r="J13" s="17"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="16">
         <v>4261</v>
       </c>
-      <c r="M13" s="12">
+      <c r="M13" s="15">
         <v>0.223147420790783</v>
       </c>
-      <c r="N13" s="13">
+      <c r="N13" s="16">
         <v>2803</v>
       </c>
-      <c r="O13" s="12">
+      <c r="O13" s="15">
         <v>0.146792354019377</v>
       </c>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="16"/>
-      <c r="V13" s="17">
+      <c r="P13" s="18"/>
+      <c r="Q13" s="15"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="15"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="21">
         <v>45839</v>
       </c>
-      <c r="W13" s="18"/>
-      <c r="X13" s="19"/>
-      <c r="Y13" s="20"/>
-      <c r="Z13" s="18"/>
-      <c r="AA13" s="19"/>
-      <c r="AB13" s="20"/>
-      <c r="AC13" s="21"/>
-      <c r="AD13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="23"/>
+      <c r="Y13" s="24"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="23"/>
+      <c r="AB13" s="24"/>
+      <c r="AC13" s="25"/>
+      <c r="AD13" s="26"/>
     </row>
     <row r="14" spans="1:30">
-      <c r="A14" s="10">
+      <c r="A14" s="13">
         <v>18687</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="14">
         <v>7446</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="15">
         <v>0.398458821640713</v>
       </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="13">
+      <c r="D14" s="16"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="16">
         <v>1900</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="15">
         <v>0.101674961202975</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="16">
         <v>358</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="15">
         <v>0.0191577032161396</v>
       </c>
-      <c r="J14" s="14"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="13">
+      <c r="J14" s="17"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="16">
         <v>6267</v>
       </c>
-      <c r="M14" s="12">
+      <c r="M14" s="15">
         <v>0.335366832557393</v>
       </c>
-      <c r="N14" s="13">
+      <c r="N14" s="16">
         <v>2716</v>
       </c>
-      <c r="O14" s="12">
+      <c r="O14" s="15">
         <v>0.145341681382779</v>
       </c>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="16"/>
-      <c r="V14" s="17">
+      <c r="P14" s="18"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="15"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="21">
         <v>45853</v>
       </c>
-      <c r="W14" s="18"/>
-      <c r="X14" s="19"/>
-      <c r="Y14" s="20"/>
-      <c r="Z14" s="18"/>
-      <c r="AA14" s="19"/>
-      <c r="AB14" s="20"/>
-      <c r="AC14" s="21"/>
-      <c r="AD14" s="22"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="23"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="22"/>
+      <c r="AA14" s="23"/>
+      <c r="AB14" s="24"/>
+      <c r="AC14" s="25"/>
+      <c r="AD14" s="26"/>
     </row>
     <row r="15" spans="1:30">
-      <c r="A15" s="10">
+      <c r="A15" s="13">
         <v>23849</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="14">
         <v>12512</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="15">
         <v>0.52463415656841</v>
       </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="13">
+      <c r="D15" s="16"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="16">
         <v>1900</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="15">
         <v>0.0796679106042182</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="16">
         <v>358</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="15">
         <v>0.0150111115770053</v>
       </c>
-      <c r="J15" s="14"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="13">
+      <c r="J15" s="17"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="16">
         <v>6253</v>
       </c>
-      <c r="M15" s="12">
+      <c r="M15" s="15">
         <v>0.262191286846409</v>
       </c>
-      <c r="N15" s="13">
+      <c r="N15" s="16">
         <v>2826</v>
       </c>
-      <c r="O15" s="12">
+      <c r="O15" s="15">
         <v>0.118495534403958</v>
       </c>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="14"/>
-      <c r="S15" s="12"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="16"/>
-      <c r="V15" s="17">
+      <c r="P15" s="18"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="15"/>
+      <c r="T15" s="19"/>
+      <c r="U15" s="20"/>
+      <c r="V15" s="21">
         <v>45870</v>
       </c>
-      <c r="W15" s="18"/>
-      <c r="X15" s="19"/>
-      <c r="Y15" s="20"/>
-      <c r="Z15" s="18"/>
-      <c r="AA15" s="19"/>
-      <c r="AB15" s="20"/>
-      <c r="AC15" s="21"/>
-      <c r="AD15" s="22"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="23"/>
+      <c r="Y15" s="24"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="23"/>
+      <c r="AB15" s="24"/>
+      <c r="AC15" s="25"/>
+      <c r="AD15" s="26"/>
     </row>
     <row r="16" spans="1:30">
-      <c r="A16" s="10">
+      <c r="A16" s="13">
         <v>23497</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="14">
         <v>11837</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="15">
         <v>0.503766438268715</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="13">
+      <c r="D16" s="16"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="16">
         <v>1900</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="15">
         <v>0.0808613865599864</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="16">
         <v>358</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="15">
         <v>0.0152359875728816</v>
       </c>
-      <c r="J16" s="14"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="13">
+      <c r="J16" s="17"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="16">
         <v>6264</v>
       </c>
-      <c r="M16" s="12">
+      <c r="M16" s="15">
         <v>0.266587223900924</v>
       </c>
-      <c r="N16" s="13">
+      <c r="N16" s="16">
         <v>3138</v>
       </c>
-      <c r="O16" s="12">
+      <c r="O16" s="15">
         <v>0.133548963697493</v>
       </c>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="14"/>
-      <c r="S16" s="12"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
-      <c r="V16" s="17">
+      <c r="P16" s="18"/>
+      <c r="Q16" s="15"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="15"/>
+      <c r="T16" s="19"/>
+      <c r="U16" s="20"/>
+      <c r="V16" s="21">
         <v>45884</v>
       </c>
-      <c r="W16" s="18"/>
-      <c r="X16" s="19"/>
-      <c r="Y16" s="20"/>
-      <c r="Z16" s="18"/>
-      <c r="AA16" s="19"/>
-      <c r="AB16" s="20"/>
-      <c r="AC16" s="21"/>
-      <c r="AD16" s="22"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="23"/>
+      <c r="Y16" s="24"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="23"/>
+      <c r="AB16" s="24"/>
+      <c r="AC16" s="25"/>
+      <c r="AD16" s="26"/>
     </row>
     <row r="17" spans="1:30">
-      <c r="A17" s="10">
+      <c r="A17" s="13">
         <v>22261</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="14">
         <v>11649</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="15">
         <v>0.523291855711783</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="13">
+      <c r="D17" s="16"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="16">
         <v>1900</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="15">
         <v>0.0853510623961188</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="16">
         <v>356</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="15">
         <v>0.0159920937963254</v>
       </c>
-      <c r="J17" s="14"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="13">
+      <c r="J17" s="17"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="16">
         <v>4215</v>
       </c>
-      <c r="M17" s="12">
+      <c r="M17" s="15">
         <v>0.189344593684021</v>
       </c>
-      <c r="N17" s="13">
+      <c r="N17" s="16">
         <v>4141</v>
       </c>
-      <c r="O17" s="12">
+      <c r="O17" s="15">
         <v>0.186020394411751</v>
       </c>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="14"/>
-      <c r="S17" s="12"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="16"/>
-      <c r="V17" s="17">
+      <c r="P17" s="18"/>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="15"/>
+      <c r="T17" s="19"/>
+      <c r="U17" s="20"/>
+      <c r="V17" s="21">
         <v>45901</v>
       </c>
-      <c r="W17" s="18"/>
-      <c r="X17" s="19"/>
-      <c r="Y17" s="20"/>
-      <c r="Z17" s="18"/>
-      <c r="AA17" s="19"/>
-      <c r="AB17" s="20"/>
-      <c r="AC17" s="21"/>
-      <c r="AD17" s="22"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="23"/>
+      <c r="Y17" s="24"/>
+      <c r="Z17" s="22"/>
+      <c r="AA17" s="23"/>
+      <c r="AB17" s="24"/>
+      <c r="AC17" s="25"/>
+      <c r="AD17" s="26"/>
     </row>
     <row r="18" spans="1:30">
-      <c r="A18" s="23">
+      <c r="A18" s="27">
         <v>21468</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="14">
         <v>9955</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="15">
         <v>0.463713433948202</v>
       </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="13">
+      <c r="D18" s="16"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="16">
         <v>1900</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="15">
         <v>0.0885038196385318</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="16">
         <v>356</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="15">
         <v>0.0165828209427986</v>
       </c>
-      <c r="J18" s="14"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="13">
+      <c r="J18" s="17"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="16">
         <v>4203</v>
       </c>
-      <c r="M18" s="12">
+      <c r="M18" s="15">
         <v>0.195779765231973</v>
       </c>
-      <c r="N18" s="13">
+      <c r="N18" s="16">
         <v>5054</v>
       </c>
-      <c r="O18" s="12">
+      <c r="O18" s="15">
         <v>0.235420160238494</v>
       </c>
-      <c r="P18" s="15">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="12">
-        <v>0</v>
-      </c>
-      <c r="R18" s="24"/>
-      <c r="S18" s="12"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="16"/>
-      <c r="V18" s="17">
+      <c r="P18" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="15">
+        <v>0</v>
+      </c>
+      <c r="R18" s="28"/>
+      <c r="S18" s="15"/>
+      <c r="T18" s="19"/>
+      <c r="U18" s="20"/>
+      <c r="V18" s="21">
         <v>45915</v>
       </c>
-      <c r="W18" s="18"/>
-      <c r="X18" s="19"/>
-      <c r="Y18" s="20"/>
-      <c r="Z18" s="18"/>
-      <c r="AA18" s="19"/>
-      <c r="AB18" s="20"/>
-      <c r="AC18" s="21"/>
-      <c r="AD18" s="22"/>
+      <c r="W18" s="22"/>
+      <c r="X18" s="23"/>
+      <c r="Y18" s="24"/>
+      <c r="Z18" s="22"/>
+      <c r="AA18" s="23"/>
+      <c r="AB18" s="24"/>
+      <c r="AC18" s="25"/>
+      <c r="AD18" s="26"/>
     </row>
     <row r="19" spans="1:30">
-      <c r="A19" s="23">
+      <c r="A19" s="27">
         <v>21356</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="14">
         <v>3229</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="15">
         <v>0.15119872635325</v>
       </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="13">
+      <c r="D19" s="16"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="16">
         <v>1000</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="15">
         <v>0.0468252481738153</v>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="16">
         <v>355</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="15">
         <v>0.0166229631017044</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="17">
         <v>7282</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="15">
         <v>0.340981457201723</v>
       </c>
-      <c r="L19" s="13">
+      <c r="L19" s="16">
         <v>4191</v>
       </c>
-      <c r="M19" s="12">
+      <c r="M19" s="15">
         <v>0.19624461509646</v>
       </c>
-      <c r="N19" s="13">
+      <c r="N19" s="16">
         <v>4899</v>
       </c>
-      <c r="O19" s="12">
+      <c r="O19" s="15">
         <v>0.229396890803521</v>
       </c>
-      <c r="P19" s="15">
+      <c r="P19" s="18">
         <v>400</v>
       </c>
-      <c r="Q19" s="12">
+      <c r="Q19" s="15">
         <v>0.0187300992695261</v>
       </c>
-      <c r="R19" s="14"/>
-      <c r="S19" s="12"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="16"/>
-      <c r="V19" s="17">
+      <c r="R19" s="17"/>
+      <c r="S19" s="15"/>
+      <c r="T19" s="19"/>
+      <c r="U19" s="20"/>
+      <c r="V19" s="21">
         <v>45931</v>
       </c>
-      <c r="W19" s="18"/>
-      <c r="X19" s="19"/>
-      <c r="Y19" s="20"/>
-      <c r="Z19" s="18"/>
-      <c r="AA19" s="19"/>
-      <c r="AB19" s="20"/>
-      <c r="AC19" s="21"/>
-      <c r="AD19" s="22"/>
+      <c r="W19" s="22"/>
+      <c r="X19" s="23"/>
+      <c r="Y19" s="24"/>
+      <c r="Z19" s="22"/>
+      <c r="AA19" s="23"/>
+      <c r="AB19" s="24"/>
+      <c r="AC19" s="25"/>
+      <c r="AD19" s="26"/>
     </row>
     <row r="20" spans="1:30">
-      <c r="A20" s="23">
+      <c r="A20" s="27">
         <v>21809</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="14">
         <v>4121</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="15">
         <v>0.188958686780687</v>
       </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="13">
+      <c r="D20" s="16"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="16">
         <v>1000</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="15">
         <v>0.0458526296483103</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="16">
         <v>356</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="15">
         <v>0.0163235361547985</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="17">
         <v>5690</v>
       </c>
-      <c r="K20" s="12">
+      <c r="K20" s="15">
         <v>0.260901462698886</v>
       </c>
-      <c r="L20" s="13">
+      <c r="L20" s="16">
         <v>4202</v>
       </c>
-      <c r="M20" s="12">
+      <c r="M20" s="15">
         <v>0.1926727497822</v>
       </c>
-      <c r="N20" s="13">
+      <c r="N20" s="16">
         <v>6040</v>
       </c>
-      <c r="O20" s="12">
+      <c r="O20" s="15">
         <v>0.276949883075794</v>
       </c>
-      <c r="P20" s="15">
+      <c r="P20" s="18">
         <v>400</v>
       </c>
-      <c r="Q20" s="12">
+      <c r="Q20" s="15">
         <v>0.0183410518593241</v>
       </c>
-      <c r="R20" s="14"/>
-      <c r="S20" s="12"/>
-      <c r="T20" s="16"/>
-      <c r="U20" s="16"/>
-      <c r="V20" s="17">
+      <c r="R20" s="17"/>
+      <c r="S20" s="15"/>
+      <c r="T20" s="19"/>
+      <c r="U20" s="20"/>
+      <c r="V20" s="21">
         <v>45945</v>
       </c>
-      <c r="W20" s="18"/>
-      <c r="X20" s="19"/>
-      <c r="Y20" s="20"/>
-      <c r="Z20" s="18"/>
-      <c r="AA20" s="19"/>
-      <c r="AB20" s="20"/>
-      <c r="AC20" s="21"/>
-      <c r="AD20" s="22"/>
+      <c r="W20" s="22"/>
+      <c r="X20" s="23"/>
+      <c r="Y20" s="24"/>
+      <c r="Z20" s="22"/>
+      <c r="AA20" s="23"/>
+      <c r="AB20" s="24"/>
+      <c r="AC20" s="25"/>
+      <c r="AD20" s="26"/>
     </row>
     <row r="21" spans="1:30">
-      <c r="A21" s="23">
+      <c r="A21" s="27">
         <v>20595</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="14">
         <v>2797</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="15">
         <v>0.135809662539451</v>
       </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="13">
+      <c r="D21" s="16"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="16">
         <v>1000</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="15">
         <v>0.0485554746297645</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="16">
         <v>354</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="15">
         <v>0.0171886380189366</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="17">
         <v>5786</v>
       </c>
-      <c r="K21" s="12">
+      <c r="K21" s="15">
         <v>0.280941976207817</v>
       </c>
-      <c r="L21" s="13">
+      <c r="L21" s="16">
         <v>4218</v>
       </c>
-      <c r="M21" s="12">
+      <c r="M21" s="15">
         <v>0.204806991988347</v>
       </c>
-      <c r="N21" s="13">
+      <c r="N21" s="16">
         <v>6040</v>
       </c>
-      <c r="O21" s="12">
+      <c r="O21" s="15">
         <v>0.293275066763778</v>
       </c>
-      <c r="P21" s="15">
+      <c r="P21" s="18">
         <v>400</v>
       </c>
-      <c r="Q21" s="12">
+      <c r="Q21" s="15">
         <v>0.0194221898519058</v>
       </c>
-      <c r="R21" s="14"/>
-      <c r="S21" s="12"/>
-      <c r="T21" s="16"/>
-      <c r="U21" s="16"/>
-      <c r="V21" s="17">
+      <c r="R21" s="17"/>
+      <c r="S21" s="15"/>
+      <c r="T21" s="19"/>
+      <c r="U21" s="20"/>
+      <c r="V21" s="21">
         <v>45962</v>
       </c>
-      <c r="W21" s="18"/>
-      <c r="X21" s="19"/>
-      <c r="Y21" s="20"/>
-      <c r="Z21" s="18"/>
-      <c r="AA21" s="19"/>
-      <c r="AB21" s="20"/>
-      <c r="AC21" s="21"/>
-      <c r="AD21" s="22"/>
+      <c r="W21" s="22"/>
+      <c r="X21" s="23"/>
+      <c r="Y21" s="24"/>
+      <c r="Z21" s="22"/>
+      <c r="AA21" s="23"/>
+      <c r="AB21" s="24"/>
+      <c r="AC21" s="25"/>
+      <c r="AD21" s="26"/>
     </row>
     <row r="22" spans="1:30">
-      <c r="A22" s="23">
+      <c r="A22" s="27">
         <v>24091</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="14">
         <v>6176</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="15">
         <v>0.256361296749824</v>
       </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="13">
+      <c r="D22" s="16"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="16">
         <v>1000</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="15">
         <v>0.0415092773234818</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="16">
         <v>354</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="15">
         <v>0.0146942841725126</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="17">
         <v>5660</v>
       </c>
-      <c r="K22" s="12">
+      <c r="K22" s="15">
         <v>0.234942509650907</v>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="16">
         <v>4227</v>
       </c>
-      <c r="M22" s="12">
+      <c r="M22" s="15">
         <v>0.175459715246358</v>
       </c>
-      <c r="N22" s="13">
+      <c r="N22" s="16">
         <v>6274</v>
       </c>
-      <c r="O22" s="12">
+      <c r="O22" s="15">
         <v>0.260429205927525</v>
       </c>
-      <c r="P22" s="15">
+      <c r="P22" s="18">
         <v>400</v>
       </c>
-      <c r="Q22" s="12">
+      <c r="Q22" s="15">
         <v>0.0166037109293927</v>
       </c>
-      <c r="R22" s="14"/>
-      <c r="S22" s="12"/>
-      <c r="T22" s="16"/>
-      <c r="U22" s="16"/>
-      <c r="V22" s="17">
+      <c r="R22" s="17"/>
+      <c r="S22" s="15"/>
+      <c r="T22" s="19"/>
+      <c r="U22" s="20"/>
+      <c r="V22" s="21">
         <v>45976</v>
       </c>
-      <c r="W22" s="25">
+      <c r="W22" s="29">
         <v>0.256361296749824</v>
       </c>
-      <c r="X22" s="16">
+      <c r="X22" s="20">
         <v>0.0562035614959944</v>
       </c>
-      <c r="Y22" s="26">
+      <c r="Y22" s="30">
         <v>0.687435141754182</v>
       </c>
-      <c r="Z22" s="16">
+      <c r="Z22" s="20">
         <v>0.341766801521647</v>
       </c>
-      <c r="AA22" s="16">
+      <c r="AA22" s="20">
         <v>0.255238210253004</v>
       </c>
-      <c r="AB22" s="27">
+      <c r="AB22" s="31">
         <v>0.402994988225349</v>
       </c>
-      <c r="AC22" s="21">
+      <c r="AC22" s="25">
         <v>16561</v>
       </c>
-      <c r="AD22" s="10"/>
+      <c r="AD22" s="13"/>
     </row>
     <row r="23" spans="1:30">
-      <c r="A23" s="23">
+      <c r="A23" s="27">
         <v>22164</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="14">
         <v>5343</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="15">
         <v>0.241066594477531</v>
       </c>
-      <c r="D23" s="13"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="13">
-        <v>0</v>
-      </c>
-      <c r="G23" s="12">
-        <v>0</v>
-      </c>
-      <c r="H23" s="13">
+      <c r="D23" s="16"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="16">
+        <v>0</v>
+      </c>
+      <c r="G23" s="15">
+        <v>0</v>
+      </c>
+      <c r="H23" s="16">
         <v>353</v>
       </c>
-      <c r="I23" s="12">
+      <c r="I23" s="15">
         <v>0.0159267280274319</v>
       </c>
-      <c r="J23" s="14">
+      <c r="J23" s="17">
         <v>5467</v>
       </c>
-      <c r="K23" s="12">
+      <c r="K23" s="15">
         <v>0.246661252481502</v>
       </c>
-      <c r="L23" s="13">
+      <c r="L23" s="16">
         <v>4221</v>
       </c>
-      <c r="M23" s="12">
+      <c r="M23" s="15">
         <v>0.190443963183541</v>
       </c>
-      <c r="N23" s="13">
+      <c r="N23" s="16">
         <v>6380</v>
       </c>
-      <c r="O23" s="12">
+      <c r="O23" s="15">
         <v>0.287854177946219</v>
       </c>
-      <c r="P23" s="15">
+      <c r="P23" s="18">
         <v>400</v>
       </c>
-      <c r="Q23" s="12">
+      <c r="Q23" s="15">
         <v>0.0180472838837755</v>
       </c>
-      <c r="R23" s="14"/>
-      <c r="S23" s="12"/>
-      <c r="T23" s="16"/>
-      <c r="U23" s="16"/>
-      <c r="V23" s="17">
+      <c r="R23" s="17"/>
+      <c r="S23" s="15"/>
+      <c r="T23" s="19"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="21">
         <v>45992</v>
       </c>
-      <c r="W23" s="25">
+      <c r="W23" s="29">
         <v>0.241066594477531</v>
       </c>
-      <c r="X23" s="16">
+      <c r="X23" s="20">
         <v>0.0159267280274319</v>
       </c>
-      <c r="Y23" s="26">
+      <c r="Y23" s="30">
         <v>0.743006677495037</v>
       </c>
-      <c r="Z23" s="16">
+      <c r="Z23" s="20">
         <v>0.331977167840661</v>
       </c>
-      <c r="AA23" s="16">
+      <c r="AA23" s="20">
         <v>0.256315278115132</v>
       </c>
-      <c r="AB23" s="27">
+      <c r="AB23" s="31">
         <v>0.411707554044207</v>
       </c>
-      <c r="AC23" s="21">
+      <c r="AC23" s="25">
         <v>16468</v>
       </c>
-      <c r="AD23" s="10"/>
+      <c r="AD23" s="13"/>
     </row>
     <row r="24" spans="1:30">
-      <c r="A24" s="23">
+      <c r="A24" s="27">
         <v>25939</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="14">
         <v>8667</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="15">
         <v>0.334130074405336</v>
       </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="13">
-        <v>0</v>
-      </c>
-      <c r="G24" s="12">
-        <v>0</v>
-      </c>
-      <c r="H24" s="13">
+      <c r="D24" s="16"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="16">
+        <v>0</v>
+      </c>
+      <c r="G24" s="15">
+        <v>0</v>
+      </c>
+      <c r="H24" s="16">
         <v>352</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="15">
         <v>0.0135702995489417</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="17">
         <v>10070</v>
       </c>
-      <c r="K24" s="12">
+      <c r="K24" s="15">
         <v>0.388218512664328</v>
       </c>
-      <c r="L24" s="13">
-        <v>0</v>
-      </c>
-      <c r="M24" s="12">
-        <v>0</v>
-      </c>
-      <c r="N24" s="13">
+      <c r="L24" s="16">
+        <v>0</v>
+      </c>
+      <c r="M24" s="15">
+        <v>0</v>
+      </c>
+      <c r="N24" s="16">
         <v>6450</v>
       </c>
-      <c r="O24" s="12">
+      <c r="O24" s="15">
         <v>0.248660318439416</v>
       </c>
-      <c r="P24" s="15">
+      <c r="P24" s="18">
         <v>400</v>
       </c>
-      <c r="Q24" s="12">
+      <c r="Q24" s="15">
         <v>0.0154207949419793</v>
       </c>
-      <c r="R24" s="14"/>
-      <c r="S24" s="12"/>
-      <c r="T24" s="16"/>
-      <c r="U24" s="16"/>
-      <c r="V24" s="17">
+      <c r="R24" s="17"/>
+      <c r="S24" s="15"/>
+      <c r="T24" s="19"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="21">
         <v>46006</v>
       </c>
-      <c r="W24" s="25">
+      <c r="W24" s="29">
         <v>0.334130074405336</v>
       </c>
-      <c r="X24" s="16">
+      <c r="X24" s="20">
         <v>0.0135702995489417</v>
       </c>
-      <c r="Y24" s="26">
+      <c r="Y24" s="30">
         <v>0.652299626045723</v>
       </c>
-      <c r="Z24" s="16">
+      <c r="Z24" s="20">
         <v>0.595153664302601</v>
       </c>
-      <c r="AA24" s="16">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="27">
+      <c r="AA24" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="31">
         <v>0.4048463356974</v>
       </c>
-      <c r="AC24" s="21">
+      <c r="AC24" s="25">
         <v>16920</v>
       </c>
-      <c r="AD24" s="22"/>
+      <c r="AD24" s="26"/>
     </row>
     <row r="25" spans="1:30">
-      <c r="A25" s="23">
+      <c r="A25" s="27">
         <v>25842</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="14">
         <v>5093</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="15">
         <v>0.197082269174213</v>
       </c>
-      <c r="D25" s="13"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="13">
-        <v>0</v>
-      </c>
-      <c r="G25" s="12">
-        <v>0</v>
-      </c>
-      <c r="H25" s="13">
+      <c r="D25" s="16"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="16">
+        <v>0</v>
+      </c>
+      <c r="G25" s="15">
+        <v>0</v>
+      </c>
+      <c r="H25" s="16">
         <v>349</v>
       </c>
-      <c r="I25" s="12">
+      <c r="I25" s="15">
         <v>0.0135051466604752</v>
       </c>
-      <c r="J25" s="14">
+      <c r="J25" s="17">
         <v>13131</v>
       </c>
-      <c r="K25" s="12">
+      <c r="K25" s="15">
         <v>0.508126306013466</v>
       </c>
-      <c r="L25" s="13">
-        <v>0</v>
-      </c>
-      <c r="M25" s="12">
-        <v>0</v>
-      </c>
-      <c r="N25" s="13">
+      <c r="L25" s="16">
+        <v>0</v>
+      </c>
+      <c r="M25" s="15">
+        <v>0</v>
+      </c>
+      <c r="N25" s="16">
         <v>6869</v>
       </c>
-      <c r="O25" s="12">
+      <c r="O25" s="15">
         <v>0.265807600030957</v>
       </c>
-      <c r="P25" s="15">
+      <c r="P25" s="18">
         <v>400</v>
       </c>
-      <c r="Q25" s="12">
+      <c r="Q25" s="15">
         <v>0.0154786781208885</v>
       </c>
-      <c r="R25" s="14"/>
-      <c r="S25" s="12"/>
-      <c r="T25" s="16"/>
-      <c r="U25" s="16"/>
-      <c r="V25" s="17">
+      <c r="R25" s="17"/>
+      <c r="S25" s="15"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="20"/>
+      <c r="V25" s="21">
         <v>46023</v>
       </c>
-      <c r="W25" s="25">
+      <c r="W25" s="29">
         <v>0.197082269174213</v>
       </c>
-      <c r="X25" s="16">
+      <c r="X25" s="20">
         <v>0.0135051466604752</v>
       </c>
-      <c r="Y25" s="26">
+      <c r="Y25" s="30">
         <v>0.789412584165312</v>
       </c>
-      <c r="Z25" s="16">
+      <c r="Z25" s="20">
         <v>0.643676470588235</v>
       </c>
-      <c r="AA25" s="16">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="27">
+      <c r="AA25" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="31">
         <v>0.356323529411765</v>
       </c>
-      <c r="AC25" s="21">
+      <c r="AC25" s="25">
         <v>20400</v>
       </c>
-      <c r="AD25" s="22"/>
+      <c r="AD25" s="26"/>
     </row>
     <row r="26" spans="1:30">
-      <c r="A26" s="23">
+      <c r="A26" s="27">
         <v>27323</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="14">
         <v>5286</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="15">
         <v>0.193463382498262</v>
       </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="13">
-        <v>0</v>
-      </c>
-      <c r="G26" s="12">
-        <v>0</v>
-      </c>
-      <c r="H26" s="13">
+      <c r="D26" s="16"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="16">
+        <v>0</v>
+      </c>
+      <c r="G26" s="15">
+        <v>0</v>
+      </c>
+      <c r="H26" s="16">
         <v>1391</v>
       </c>
-      <c r="I26" s="12">
+      <c r="I26" s="15">
         <v>0.0509094901731142</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="17">
         <v>12835</v>
       </c>
-      <c r="K26" s="12">
+      <c r="K26" s="15">
         <v>0.469750759433444</v>
       </c>
-      <c r="L26" s="13">
-        <v>0</v>
-      </c>
-      <c r="M26" s="12">
-        <v>0</v>
-      </c>
-      <c r="N26" s="13">
+      <c r="L26" s="16">
+        <v>0</v>
+      </c>
+      <c r="M26" s="15">
+        <v>0</v>
+      </c>
+      <c r="N26" s="16">
         <v>7411</v>
       </c>
-      <c r="O26" s="12">
+      <c r="O26" s="15">
         <v>0.271236687040223</v>
       </c>
-      <c r="P26" s="15">
+      <c r="P26" s="18">
         <v>400</v>
       </c>
-      <c r="Q26" s="12">
+      <c r="Q26" s="15">
         <v>0.0146396808549574</v>
       </c>
-      <c r="R26" s="14"/>
-      <c r="S26" s="12"/>
-      <c r="T26" s="16"/>
-      <c r="U26" s="16"/>
-      <c r="V26" s="17">
+      <c r="R26" s="17"/>
+      <c r="S26" s="15"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="20"/>
+      <c r="V26" s="21">
         <v>46037</v>
       </c>
-      <c r="W26" s="25">
+      <c r="W26" s="29">
         <v>0.193463382498262</v>
       </c>
-      <c r="X26" s="16">
+      <c r="X26" s="20">
         <v>0.0509094901731142</v>
       </c>
-      <c r="Y26" s="26">
+      <c r="Y26" s="30">
         <v>0.755627127328624</v>
       </c>
-      <c r="Z26" s="16">
+      <c r="Z26" s="20">
         <v>0.621670057153928</v>
       </c>
-      <c r="AA26" s="16">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="27">
+      <c r="AA26" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="31">
         <v>0.378329942846072</v>
       </c>
-      <c r="AC26" s="14">
+      <c r="AC26" s="17">
         <v>20646</v>
       </c>
-      <c r="AD26" s="22"/>
+      <c r="AD26" s="26"/>
     </row>
     <row r="27" spans="1:30">
-      <c r="A27" s="23">
+      <c r="A27" s="27">
         <v>25699</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="14">
         <v>3500</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="15">
         <v>0.13619206973034</v>
       </c>
-      <c r="D27" s="13"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="13">
-        <v>0</v>
-      </c>
-      <c r="G27" s="12">
-        <v>0</v>
-      </c>
-      <c r="H27" s="13">
+      <c r="D27" s="16"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="16">
+        <v>0</v>
+      </c>
+      <c r="G27" s="15">
+        <v>0</v>
+      </c>
+      <c r="H27" s="16">
         <v>1388</v>
       </c>
-      <c r="I27" s="12">
+      <c r="I27" s="15">
         <v>0.0540098836530604</v>
       </c>
-      <c r="J27" s="14">
+      <c r="J27" s="17">
         <v>12741</v>
       </c>
-      <c r="K27" s="12">
+      <c r="K27" s="15">
         <v>0.495778045838359</v>
       </c>
-      <c r="L27" s="13">
-        <v>0</v>
-      </c>
-      <c r="M27" s="12">
-        <v>0</v>
-      </c>
-      <c r="N27" s="13">
+      <c r="L27" s="16">
+        <v>0</v>
+      </c>
+      <c r="M27" s="15">
+        <v>0</v>
+      </c>
+      <c r="N27" s="16">
         <v>7670</v>
       </c>
-      <c r="O27" s="12">
+      <c r="O27" s="15">
         <v>0.298455192809059</v>
       </c>
-      <c r="P27" s="15">
+      <c r="P27" s="18">
         <v>400</v>
       </c>
-      <c r="Q27" s="12">
+      <c r="Q27" s="15">
         <v>0.0155648079691817</v>
       </c>
-      <c r="R27" s="14"/>
-      <c r="S27" s="12"/>
-      <c r="T27" s="16"/>
-      <c r="U27" s="16"/>
-      <c r="V27" s="17">
+      <c r="R27" s="17"/>
+      <c r="S27" s="15"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="20"/>
+      <c r="V27" s="21">
         <v>46054</v>
       </c>
-      <c r="W27" s="25">
+      <c r="W27" s="29">
         <v>0.13619206973034</v>
       </c>
-      <c r="X27" s="16">
+      <c r="X27" s="20">
         <v>0.0540098836530604</v>
       </c>
-      <c r="Y27" s="26">
+      <c r="Y27" s="30">
         <v>0.8097980466166</v>
       </c>
-      <c r="Z27" s="16">
+      <c r="Z27" s="20">
         <v>0.612224304454375</v>
       </c>
-      <c r="AA27" s="16">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="27">
+      <c r="AA27" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="31">
         <v>0.387775695545625</v>
       </c>
-      <c r="AC27" s="14">
+      <c r="AC27" s="17">
         <v>20811</v>
       </c>
-      <c r="AD27" s="22"/>
+      <c r="AD27" s="26"/>
     </row>
     <row r="28" spans="1:30">
-      <c r="A28" s="23">
+      <c r="A28" s="27">
         <v>28281</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="14">
         <v>1573</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="15">
         <v>0.0556203811746402</v>
       </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="13">
+      <c r="D28" s="16"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="16">
         <v>4700</v>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="15">
         <v>0.16618931438068</v>
       </c>
-      <c r="H28" s="13">
+      <c r="H28" s="16">
         <v>1378</v>
       </c>
-      <c r="I28" s="12">
+      <c r="I28" s="15">
         <v>0.0487252925992716</v>
       </c>
-      <c r="J28" s="14">
+      <c r="J28" s="17">
         <v>12285</v>
       </c>
-      <c r="K28" s="12">
+      <c r="K28" s="15">
         <v>0.434390580248223</v>
       </c>
-      <c r="L28" s="13">
-        <v>0</v>
-      </c>
-      <c r="M28" s="12">
-        <v>0</v>
-      </c>
-      <c r="N28" s="13">
+      <c r="L28" s="16">
+        <v>0</v>
+      </c>
+      <c r="M28" s="15">
+        <v>0</v>
+      </c>
+      <c r="N28" s="16">
         <v>7945</v>
       </c>
-      <c r="O28" s="12">
+      <c r="O28" s="15">
         <v>0.280930660160532</v>
       </c>
-      <c r="P28" s="15">
+      <c r="P28" s="18">
         <v>400</v>
       </c>
-      <c r="Q28" s="12">
+      <c r="Q28" s="15">
         <v>0.0141437714366536</v>
       </c>
-      <c r="R28" s="14"/>
-      <c r="S28" s="12"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="16"/>
-      <c r="V28" s="17">
+      <c r="R28" s="17"/>
+      <c r="S28" s="15"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="20"/>
+      <c r="V28" s="21">
         <v>46068</v>
       </c>
-      <c r="W28" s="25">
+      <c r="W28" s="29">
         <v>0.0556203811746402</v>
       </c>
-      <c r="X28" s="16">
+      <c r="X28" s="20">
         <v>0.214914606979951</v>
       </c>
-      <c r="Y28" s="26">
+      <c r="Y28" s="30">
         <v>0.729465011845409</v>
       </c>
-      <c r="Z28" s="16">
+      <c r="Z28" s="20">
         <v>0.595492001938924</v>
       </c>
-      <c r="AA28" s="16">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="27">
+      <c r="AA28" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="31">
         <v>0.404507998061076</v>
       </c>
-      <c r="AC28" s="14">
+      <c r="AC28" s="17">
         <v>20630</v>
       </c>
-      <c r="AD28" s="22"/>
+      <c r="AD28" s="26"/>
     </row>
     <row r="29" spans="1:30">
-      <c r="A29" s="23">
+      <c r="A29" s="27">
         <v>32195</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="14">
         <v>1348</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="15">
         <v>0.0418698555676347</v>
       </c>
-      <c r="D29" s="13">
+      <c r="D29" s="16">
         <v>4000</v>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="15">
         <v>0.12424289485945</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="16">
         <v>4700</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="15">
         <v>0.145985401459854</v>
       </c>
-      <c r="H29" s="13">
+      <c r="H29" s="16">
         <v>1369</v>
       </c>
-      <c r="I29" s="12">
+      <c r="I29" s="15">
         <v>0.0425221307656468</v>
       </c>
-      <c r="J29" s="14">
+      <c r="J29" s="17">
         <v>11847</v>
       </c>
-      <c r="K29" s="12">
+      <c r="K29" s="15">
         <v>0.367976393849977</v>
       </c>
-      <c r="L29" s="13">
-        <v>0</v>
-      </c>
-      <c r="M29" s="12">
-        <v>0</v>
-      </c>
-      <c r="N29" s="13">
+      <c r="L29" s="16">
+        <v>0</v>
+      </c>
+      <c r="M29" s="15">
+        <v>0</v>
+      </c>
+      <c r="N29" s="16">
         <v>8531</v>
       </c>
-      <c r="O29" s="12">
+      <c r="O29" s="15">
         <v>0.264979034011492</v>
       </c>
-      <c r="P29" s="15">
+      <c r="P29" s="18">
         <v>400</v>
       </c>
-      <c r="Q29" s="12">
+      <c r="Q29" s="15">
         <v>0.012424289485945</v>
       </c>
-      <c r="R29" s="14"/>
-      <c r="S29" s="12"/>
-      <c r="T29" s="16"/>
-      <c r="U29" s="16"/>
-      <c r="V29" s="17">
+      <c r="R29" s="17"/>
+      <c r="S29" s="15"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="21">
         <v>46082</v>
       </c>
-      <c r="W29" s="25">
+      <c r="W29" s="29">
         <v>0.166112750427085</v>
       </c>
-      <c r="X29" s="16">
+      <c r="X29" s="20">
         <v>0.188507532225501</v>
       </c>
-      <c r="Y29" s="26">
+      <c r="Y29" s="30">
         <v>0.645379717347414</v>
       </c>
-      <c r="Z29" s="16">
+      <c r="Z29" s="20">
         <v>0.570170372509385</v>
       </c>
-      <c r="AA29" s="16">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="27">
+      <c r="AA29" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="31">
         <v>0.429829627490615</v>
       </c>
-      <c r="AC29" s="14">
+      <c r="AC29" s="17">
         <v>20778</v>
       </c>
-      <c r="AD29" s="22"/>
+      <c r="AD29" s="26"/>
     </row>
     <row r="30" spans="1:30">
-      <c r="A30" s="23">
+      <c r="A30" s="27">
         <v>37977</v>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="14">
         <v>1920</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="15">
         <v>0.0505569160281223</v>
       </c>
-      <c r="D30" s="13">
+      <c r="D30" s="16">
         <v>6003</v>
       </c>
-      <c r="E30" s="12">
+      <c r="E30" s="15">
         <v>0.158069357769176</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="16">
         <v>6700</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="15">
         <v>0.176422571556468</v>
       </c>
-      <c r="H30" s="13">
+      <c r="H30" s="16">
         <v>2893</v>
       </c>
-      <c r="I30" s="12">
+      <c r="I30" s="15">
         <v>0.0761776864944572</v>
       </c>
-      <c r="J30" s="14">
+      <c r="J30" s="17">
         <v>10913</v>
       </c>
-      <c r="K30" s="12">
+      <c r="K30" s="15">
         <v>0.28735813782026</v>
       </c>
-      <c r="L30" s="13">
-        <v>0</v>
-      </c>
-      <c r="M30" s="12">
-        <v>0</v>
-      </c>
-      <c r="N30" s="13">
+      <c r="L30" s="16">
+        <v>0</v>
+      </c>
+      <c r="M30" s="15">
+        <v>0</v>
+      </c>
+      <c r="N30" s="16">
         <v>9148</v>
       </c>
-      <c r="O30" s="12">
+      <c r="O30" s="15">
         <v>0.240882639492324</v>
       </c>
-      <c r="P30" s="15">
+      <c r="P30" s="18">
         <v>400</v>
       </c>
-      <c r="Q30" s="12">
+      <c r="Q30" s="15">
         <v>0.0105326908391921</v>
       </c>
-      <c r="R30" s="14"/>
-      <c r="S30" s="12"/>
-      <c r="T30" s="16"/>
-      <c r="U30" s="16"/>
-      <c r="V30" s="17">
+      <c r="R30" s="17"/>
+      <c r="S30" s="15"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="20"/>
+      <c r="V30" s="21">
         <v>46096</v>
       </c>
-      <c r="W30" s="25">
+      <c r="W30" s="29">
         <v>0.208626273797298</v>
       </c>
-      <c r="X30" s="16">
+      <c r="X30" s="20">
         <v>0.252600258050926</v>
       </c>
-      <c r="Y30" s="26">
+      <c r="Y30" s="30">
         <v>0.538773468151776</v>
       </c>
-      <c r="Z30" s="16">
+      <c r="Z30" s="20">
         <v>0.533356140951078</v>
       </c>
-      <c r="AA30" s="16">
-        <v>0</v>
-      </c>
-      <c r="AB30" s="27">
+      <c r="AA30" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="31">
         <v>0.466643859048922</v>
       </c>
-      <c r="AC30" s="14">
+      <c r="AC30" s="17">
         <v>20461</v>
       </c>
-      <c r="AD30" s="22"/>
+      <c r="AD30" s="26"/>
     </row>
     <row r="31" spans="1:30">
-      <c r="A31" s="23">
+      <c r="A31" s="27">
         <v>34800</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="14">
         <v>5</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="15">
         <v>0.00014367816091954</v>
       </c>
-      <c r="D31" s="13">
+      <c r="D31" s="16">
         <v>5080</v>
       </c>
-      <c r="E31" s="12">
+      <c r="E31" s="15">
         <v>0.145977011494253</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="16">
         <v>6700</v>
       </c>
-      <c r="G31" s="12">
+      <c r="G31" s="15">
         <v>0.192528735632184</v>
       </c>
-      <c r="H31" s="13">
+      <c r="H31" s="16">
         <v>2894</v>
       </c>
-      <c r="I31" s="12">
+      <c r="I31" s="15">
         <v>0.0831609195402299</v>
       </c>
-      <c r="J31" s="14">
+      <c r="J31" s="17">
         <v>13510</v>
       </c>
-      <c r="K31" s="12">
+      <c r="K31" s="15">
         <v>0.388218390804598</v>
       </c>
-      <c r="L31" s="13">
-        <v>0</v>
-      </c>
-      <c r="M31" s="12">
-        <v>0</v>
-      </c>
-      <c r="N31" s="13">
+      <c r="L31" s="16">
+        <v>0</v>
+      </c>
+      <c r="M31" s="15">
+        <v>0</v>
+      </c>
+      <c r="N31" s="16">
         <v>6211</v>
       </c>
-      <c r="O31" s="12">
+      <c r="O31" s="15">
         <v>0.178477011494253</v>
       </c>
-      <c r="P31" s="15">
+      <c r="P31" s="18">
         <v>400</v>
       </c>
-      <c r="Q31" s="12">
+      <c r="Q31" s="15">
         <v>0.0114942528735632</v>
       </c>
-      <c r="R31" s="14"/>
-      <c r="S31" s="12"/>
-      <c r="T31" s="16"/>
-      <c r="U31" s="16"/>
-      <c r="V31" s="17">
+      <c r="R31" s="17"/>
+      <c r="S31" s="15"/>
+      <c r="T31" s="19"/>
+      <c r="U31" s="20"/>
+      <c r="V31" s="21">
         <v>46113</v>
       </c>
-      <c r="W31" s="25">
+      <c r="W31" s="29">
         <v>0.146120689655172</v>
       </c>
-      <c r="X31" s="16">
+      <c r="X31" s="20">
         <v>0.275689655172414</v>
       </c>
-      <c r="Y31" s="26">
+      <c r="Y31" s="30">
         <v>0.578189655172414</v>
       </c>
-      <c r="Z31" s="16">
+      <c r="Z31" s="20">
         <v>0.671437801302122</v>
       </c>
-      <c r="AA31" s="16">
-        <v>0</v>
-      </c>
-      <c r="AB31" s="27">
+      <c r="AA31" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="31">
         <v>0.328562198697878</v>
       </c>
-      <c r="AC31" s="14">
+      <c r="AC31" s="17">
         <v>20121</v>
       </c>
-      <c r="AD31" s="22"/>
+      <c r="AD31" s="26"/>
     </row>
     <row r="32" spans="1:30">
-      <c r="A32" s="23">
+      <c r="A32" s="27">
         <v>36972</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="14">
         <v>21</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="15">
         <v>0.000567997403440441</v>
       </c>
-      <c r="D32" s="13">
+      <c r="D32" s="16">
         <v>4979</v>
       </c>
-      <c r="E32" s="12">
+      <c r="E32" s="15">
         <v>0.134669479606188</v>
       </c>
-      <c r="F32" s="13">
+      <c r="F32" s="16">
         <v>7700</v>
       </c>
-      <c r="G32" s="12">
+      <c r="G32" s="15">
         <v>0.208265714594829</v>
       </c>
-      <c r="H32" s="13">
+      <c r="H32" s="16">
         <v>3878</v>
       </c>
-      <c r="I32" s="12">
+      <c r="I32" s="15">
         <v>0.104890187168668</v>
       </c>
-      <c r="J32" s="14">
+      <c r="J32" s="17">
         <v>12773</v>
       </c>
-      <c r="K32" s="12">
+      <c r="K32" s="15">
         <v>0.345477658768798</v>
       </c>
-      <c r="L32" s="13">
-        <v>0</v>
-      </c>
-      <c r="M32" s="12">
-        <v>0</v>
-      </c>
-      <c r="N32" s="13">
+      <c r="L32" s="16">
+        <v>0</v>
+      </c>
+      <c r="M32" s="15">
+        <v>0</v>
+      </c>
+      <c r="N32" s="16">
         <v>7221</v>
       </c>
-      <c r="O32" s="12">
+      <c r="O32" s="15">
         <v>0.195309964297306</v>
       </c>
-      <c r="P32" s="15">
+      <c r="P32" s="18">
         <v>400</v>
       </c>
-      <c r="Q32" s="12">
+      <c r="Q32" s="15">
         <v>0.0108189981607703</v>
       </c>
-      <c r="R32" s="14"/>
-      <c r="S32" s="12"/>
-      <c r="T32" s="16"/>
-      <c r="U32" s="16"/>
-      <c r="V32" s="17">
+      <c r="R32" s="17"/>
+      <c r="S32" s="15"/>
+      <c r="T32" s="19"/>
+      <c r="U32" s="20"/>
+      <c r="V32" s="21">
         <v>46127</v>
       </c>
-      <c r="W32" s="25">
+      <c r="W32" s="29">
         <v>0.135237477009629</v>
       </c>
-      <c r="X32" s="16">
+      <c r="X32" s="20">
         <v>0.313155901763497</v>
       </c>
-      <c r="Y32" s="26">
+      <c r="Y32" s="30">
         <v>0.551606621226874</v>
       </c>
-      <c r="Z32" s="16">
+      <c r="Z32" s="20">
         <v>0.626311660292243</v>
       </c>
-      <c r="AA32" s="16">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="27">
+      <c r="AA32" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="31">
         <v>0.373688339707757</v>
       </c>
-      <c r="AC32" s="14">
+      <c r="AC32" s="17">
         <v>20394</v>
       </c>
-      <c r="AD32" s="22"/>
+      <c r="AD32" s="26"/>
     </row>
     <row r="33" spans="1:30">
-      <c r="A33" s="23">
+      <c r="A33" s="27">
         <v>34223</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="14">
         <v>949</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="15">
         <v>0.0277298892557637</v>
       </c>
-      <c r="D33" s="13">
+      <c r="D33" s="16">
         <v>1117</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="15">
         <v>0.0326388685971423</v>
       </c>
-      <c r="F33" s="13">
+      <c r="F33" s="16">
         <v>7700</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="15">
         <v>0.224994886479853</v>
       </c>
-      <c r="H33" s="13">
+      <c r="H33" s="16">
         <v>3883</v>
       </c>
-      <c r="I33" s="12">
+      <c r="I33" s="15">
         <v>0.113461707039126</v>
       </c>
-      <c r="J33" s="14">
+      <c r="J33" s="17">
         <v>12529</v>
       </c>
-      <c r="K33" s="12">
+      <c r="K33" s="15">
         <v>0.36609882242936</v>
       </c>
-      <c r="L33" s="13">
-        <v>0</v>
-      </c>
-      <c r="M33" s="12">
-        <v>0</v>
-      </c>
-      <c r="N33" s="13">
+      <c r="L33" s="16">
+        <v>0</v>
+      </c>
+      <c r="M33" s="15">
+        <v>0</v>
+      </c>
+      <c r="N33" s="16">
         <v>7645</v>
       </c>
-      <c r="O33" s="12">
+      <c r="O33" s="15">
         <v>0.223387780147854</v>
       </c>
-      <c r="P33" s="15">
+      <c r="P33" s="18">
         <v>400</v>
       </c>
-      <c r="Q33" s="12">
+      <c r="Q33" s="15">
         <v>0.0116880460509014</v>
       </c>
-      <c r="R33" s="14"/>
-      <c r="S33" s="12"/>
-      <c r="T33" s="16"/>
-      <c r="U33" s="16"/>
-      <c r="V33" s="17">
+      <c r="R33" s="17"/>
+      <c r="S33" s="15"/>
+      <c r="T33" s="19"/>
+      <c r="U33" s="20"/>
+      <c r="V33" s="21">
         <v>46143</v>
       </c>
-      <c r="W33" s="25">
+      <c r="W33" s="29">
         <v>0.0603687578529059</v>
       </c>
-      <c r="X33" s="16">
+      <c r="X33" s="20">
         <v>0.338456593518978</v>
       </c>
-      <c r="Y33" s="26">
+      <c r="Y33" s="30">
         <v>0.601174648628116</v>
       </c>
-      <c r="Z33" s="16">
+      <c r="Z33" s="20">
         <v>0.608972489549917</v>
       </c>
-      <c r="AA33" s="16">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="27">
+      <c r="AA33" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="31">
         <v>0.391027510450083</v>
       </c>
-      <c r="AC33" s="14">
+      <c r="AC33" s="17">
         <v>20574</v>
       </c>
-      <c r="AD33" s="22"/>
+      <c r="AD33" s="26"/>
     </row>
     <row r="34" spans="1:30">
-      <c r="A34" s="23">
+      <c r="A34" s="27">
         <v>37370</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="14">
         <v>1330</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="15">
         <v>0.0355900454910356</v>
       </c>
-      <c r="D34" s="13">
+      <c r="D34" s="16">
         <v>2333</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="15">
         <v>0.0624297564891624</v>
       </c>
-      <c r="F34" s="13">
+      <c r="F34" s="16">
         <v>7700</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="15">
         <v>0.206047631790206</v>
       </c>
-      <c r="H34" s="13">
+      <c r="H34" s="16">
         <v>5230</v>
       </c>
-      <c r="I34" s="12">
+      <c r="I34" s="15">
         <v>0.13995183302114</v>
       </c>
-      <c r="J34" s="14">
+      <c r="J34" s="17">
         <v>13133</v>
       </c>
-      <c r="K34" s="12">
+      <c r="K34" s="15">
         <v>0.351431629649451</v>
       </c>
-      <c r="L34" s="13">
-        <v>0</v>
-      </c>
-      <c r="M34" s="12">
-        <v>0</v>
-      </c>
-      <c r="N34" s="13">
+      <c r="L34" s="16">
+        <v>0</v>
+      </c>
+      <c r="M34" s="15">
+        <v>0</v>
+      </c>
+      <c r="N34" s="16">
         <v>7244</v>
       </c>
-      <c r="O34" s="12">
+      <c r="O34" s="15">
         <v>0.193845330478994</v>
       </c>
-      <c r="P34" s="15">
+      <c r="P34" s="18">
         <v>400</v>
       </c>
-      <c r="Q34" s="12">
+      <c r="Q34" s="15">
         <v>0.0107037730800107</v>
       </c>
-      <c r="R34" s="14"/>
-      <c r="S34" s="12"/>
-      <c r="T34" s="16"/>
-      <c r="U34" s="16"/>
-      <c r="V34" s="17">
+      <c r="R34" s="17"/>
+      <c r="S34" s="15"/>
+      <c r="T34" s="19"/>
+      <c r="U34" s="20"/>
+      <c r="V34" s="21">
         <v>46157</v>
       </c>
-      <c r="W34" s="25">
+      <c r="W34" s="29">
         <v>0.098019801980198</v>
       </c>
-      <c r="X34" s="16">
+      <c r="X34" s="20">
         <v>0.345999464811346</v>
       </c>
-      <c r="Y34" s="26">
+      <c r="Y34" s="30">
         <v>0.555980733208456</v>
       </c>
-      <c r="Z34" s="16">
+      <c r="Z34" s="20">
         <v>0.632093179958608</v>
       </c>
-      <c r="AA34" s="16">
-        <v>0</v>
-      </c>
-      <c r="AB34" s="27">
+      <c r="AA34" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="31">
         <v>0.367906820041392</v>
       </c>
-      <c r="AC34" s="14">
+      <c r="AC34" s="17">
         <v>20777</v>
       </c>
-      <c r="AD34" s="22"/>
+      <c r="AD34" s="26"/>
     </row>
     <row r="35" spans="1:30">
-      <c r="A35" s="23">
+      <c r="A35" s="27">
         <v>36079</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="14">
         <v>100</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="15">
         <v>0.00277169544610438</v>
       </c>
-      <c r="D35" s="13">
+      <c r="D35" s="16">
         <v>2334</v>
       </c>
-      <c r="E35" s="12">
+      <c r="E35" s="15">
         <v>0.0646913717120763</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F35" s="16">
         <v>7700</v>
       </c>
-      <c r="G35" s="12">
+      <c r="G35" s="15">
         <v>0.213420549350037</v>
       </c>
-      <c r="H35" s="13">
+      <c r="H35" s="16">
         <v>5217</v>
       </c>
-      <c r="I35" s="12">
+      <c r="I35" s="15">
         <v>0.144599351423266</v>
       </c>
-      <c r="J35" s="14">
+      <c r="J35" s="17">
         <v>12690</v>
       </c>
-      <c r="K35" s="12">
+      <c r="K35" s="15">
         <v>0.351728152110646</v>
       </c>
-      <c r="L35" s="13">
-        <v>0</v>
-      </c>
-      <c r="M35" s="12">
-        <v>0</v>
-      </c>
-      <c r="N35" s="13">
+      <c r="L35" s="16">
+        <v>0</v>
+      </c>
+      <c r="M35" s="15">
+        <v>0</v>
+      </c>
+      <c r="N35" s="16">
         <v>7638</v>
       </c>
-      <c r="O35" s="12">
+      <c r="O35" s="15">
         <v>0.211702098173453</v>
       </c>
-      <c r="P35" s="15">
+      <c r="P35" s="18">
         <v>400</v>
       </c>
-      <c r="Q35" s="12">
+      <c r="Q35" s="15">
         <v>0.0110867817844175</v>
       </c>
-      <c r="R35" s="14"/>
-      <c r="S35" s="12"/>
-      <c r="T35" s="16"/>
-      <c r="U35" s="16"/>
-      <c r="V35" s="17">
+      <c r="R35" s="17"/>
+      <c r="S35" s="15"/>
+      <c r="T35" s="19"/>
+      <c r="U35" s="20"/>
+      <c r="V35" s="21">
         <v>46174</v>
       </c>
-      <c r="W35" s="25">
+      <c r="W35" s="29">
         <v>0.0674630671581807</v>
       </c>
-      <c r="X35" s="16">
+      <c r="X35" s="20">
         <v>0.358019900773303</v>
       </c>
-      <c r="Y35" s="26">
+      <c r="Y35" s="30">
         <v>0.574517032068516</v>
       </c>
-      <c r="Z35" s="16">
+      <c r="Z35" s="20">
         <v>0.612215360864531</v>
       </c>
-      <c r="AA35" s="16">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="27">
+      <c r="AA35" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="31">
         <v>0.387784639135469</v>
       </c>
-      <c r="AC35" s="14">
+      <c r="AC35" s="17">
         <v>20728</v>
       </c>
-      <c r="AD35" s="22"/>
+      <c r="AD35" s="26"/>
     </row>
     <row r="36" spans="1:30">
-      <c r="A36" s="23">
+      <c r="A36" s="27">
         <v>37240</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="14">
         <v>2294</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="15">
         <v>0.0616004296455424</v>
       </c>
-      <c r="D36" s="13">
+      <c r="D36" s="16">
         <v>1556</v>
       </c>
-      <c r="E36" s="12">
+      <c r="E36" s="15">
         <v>0.0417830290010741</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="16">
         <v>7700</v>
       </c>
-      <c r="G36" s="12">
+      <c r="G36" s="15">
         <v>0.206766917293233</v>
       </c>
-      <c r="H36" s="13">
+      <c r="H36" s="16">
         <v>5194</v>
       </c>
-      <c r="I36" s="12">
+      <c r="I36" s="15">
         <v>0.139473684210526</v>
       </c>
-      <c r="J36" s="14">
+      <c r="J36" s="17">
         <v>6525</v>
       </c>
-      <c r="K36" s="12">
+      <c r="K36" s="15">
         <v>0.175214822771214</v>
       </c>
-      <c r="L36" s="13">
+      <c r="L36" s="16">
         <v>5000</v>
       </c>
-      <c r="M36" s="12">
+      <c r="M36" s="15">
         <v>0.134264232008593</v>
       </c>
-      <c r="N36" s="13">
+      <c r="N36" s="16">
         <v>8571</v>
       </c>
-      <c r="O36" s="12">
+      <c r="O36" s="15">
         <v>0.23015574650913</v>
       </c>
-      <c r="P36" s="15">
+      <c r="P36" s="18">
         <v>400</v>
       </c>
-      <c r="Q36" s="12">
+      <c r="Q36" s="15">
         <v>0.0107411385606874</v>
       </c>
-      <c r="R36" s="14"/>
-      <c r="S36" s="12"/>
-      <c r="T36" s="16"/>
-      <c r="U36" s="16"/>
-      <c r="V36" s="17">
+      <c r="R36" s="17"/>
+      <c r="S36" s="15"/>
+      <c r="T36" s="19">
+        <v>7152</v>
+      </c>
+      <c r="U36" s="20"/>
+      <c r="V36" s="21">
         <v>46188</v>
       </c>
-      <c r="W36" s="25">
+      <c r="W36" s="29">
         <v>0.103383458646617</v>
       </c>
-      <c r="X36" s="16">
+      <c r="X36" s="20">
         <v>0.346240601503759</v>
       </c>
-      <c r="Y36" s="26">
+      <c r="Y36" s="30">
         <v>0.550375939849624</v>
       </c>
-      <c r="Z36" s="16">
+      <c r="Z36" s="20">
         <v>0.318354800936768</v>
       </c>
-      <c r="AA36" s="16">
+      <c r="AA36" s="20">
         <v>0.243950039032006</v>
       </c>
-      <c r="AB36" s="27">
+      <c r="AB36" s="31">
         <v>0.437695160031226</v>
       </c>
-      <c r="AC36" s="14">
+      <c r="AC36" s="17">
         <v>20496</v>
       </c>
-      <c r="AD36" s="22"/>
+      <c r="AD36" s="26"/>
     </row>
     <row r="37" spans="1:30">
-      <c r="A37" s="23">
+      <c r="A37" s="27">
         <v>34627</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="14">
         <v>767</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="15">
         <v>0.0221503451064198</v>
       </c>
-      <c r="D37" s="13">
+      <c r="D37" s="16">
         <v>328</v>
       </c>
-      <c r="E37" s="12">
+      <c r="E37" s="15">
         <v>0.00947237704681318</v>
       </c>
-      <c r="F37" s="13">
+      <c r="F37" s="16">
         <v>7700</v>
       </c>
-      <c r="G37" s="12">
+      <c r="G37" s="15">
         <v>0.222369827013602</v>
       </c>
-      <c r="H37" s="13">
+      <c r="H37" s="16">
         <v>5222</v>
       </c>
-      <c r="I37" s="12">
+      <c r="I37" s="15">
         <v>0.150807173592861</v>
       </c>
-      <c r="J37" s="14">
+      <c r="J37" s="17">
         <v>6255</v>
       </c>
-      <c r="K37" s="12">
+      <c r="K37" s="15">
         <v>0.18063938545066</v>
       </c>
-      <c r="L37" s="13">
+      <c r="L37" s="16">
         <v>5007</v>
       </c>
-      <c r="M37" s="12">
+      <c r="M37" s="15">
         <v>0.144598145955468</v>
       </c>
-      <c r="N37" s="13">
+      <c r="N37" s="16">
         <v>8948</v>
       </c>
-      <c r="O37" s="12">
+      <c r="O37" s="15">
         <v>0.258411066508794</v>
       </c>
-      <c r="P37" s="15">
+      <c r="P37" s="18">
         <v>400</v>
       </c>
-      <c r="Q37" s="12">
+      <c r="Q37" s="15">
         <v>0.0115516793253819</v>
       </c>
-      <c r="R37" s="14"/>
-      <c r="S37" s="12"/>
-      <c r="T37" s="16"/>
-      <c r="U37" s="16"/>
-      <c r="V37" s="17">
+      <c r="R37" s="17"/>
+      <c r="S37" s="15"/>
+      <c r="T37" s="19">
+        <v>6854</v>
+      </c>
+      <c r="U37" s="20"/>
+      <c r="V37" s="21">
         <v>46204</v>
       </c>
-      <c r="W37" s="25">
+      <c r="W37" s="29">
         <v>0.031622722153233</v>
       </c>
-      <c r="X37" s="16">
+      <c r="X37" s="20">
         <v>0.373177000606463</v>
       </c>
-      <c r="Y37" s="26">
+      <c r="Y37" s="30">
         <v>0.595200277240304</v>
       </c>
-      <c r="Z37" s="16">
+      <c r="Z37" s="20">
         <v>0.303493449781659</v>
       </c>
-      <c r="AA37" s="16">
+      <c r="AA37" s="20">
         <v>0.242940320232897</v>
       </c>
-      <c r="AB37" s="27">
+      <c r="AB37" s="31">
         <v>0.453566229985444</v>
       </c>
-      <c r="AC37" s="14">
+      <c r="AC37" s="17">
         <v>20610</v>
       </c>
-      <c r="AD37" s="22"/>
+      <c r="AD37" s="26"/>
     </row>
     <row r="38" spans="1:30">
-      <c r="A38" s="23">
+      <c r="A38" s="27">
         <v>33067</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="14">
         <v>4151</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="15">
         <v>0.125533008739831</v>
       </c>
-      <c r="D38" s="13">
+      <c r="D38" s="16">
         <v>31</v>
       </c>
-      <c r="E38" s="12">
+      <c r="E38" s="15">
         <v>0.000937490549490429</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38" s="16">
         <v>7700</v>
       </c>
-      <c r="G38" s="12">
+      <c r="G38" s="15">
         <v>0.232860555841171</v>
       </c>
-      <c r="H38" s="13">
+      <c r="H38" s="16">
         <v>339</v>
       </c>
-      <c r="I38" s="12">
+      <c r="I38" s="15">
         <v>0.0102519127831373</v>
       </c>
-      <c r="J38" s="14">
+      <c r="J38" s="17">
         <v>5480</v>
       </c>
-      <c r="K38" s="12">
+      <c r="K38" s="15">
         <v>0.165724135845405</v>
       </c>
-      <c r="L38" s="13">
+      <c r="L38" s="16">
         <v>5011</v>
       </c>
-      <c r="M38" s="12">
+      <c r="M38" s="15">
         <v>0.151540811080533</v>
       </c>
-      <c r="N38" s="13">
+      <c r="N38" s="16">
         <v>9955</v>
       </c>
-      <c r="O38" s="12">
+      <c r="O38" s="15">
         <v>0.301055432908942</v>
       </c>
-      <c r="P38" s="15">
+      <c r="P38" s="18">
         <v>400</v>
       </c>
-      <c r="Q38" s="12">
+      <c r="Q38" s="15">
         <v>0.0120966522514894</v>
       </c>
-      <c r="R38" s="14"/>
-      <c r="S38" s="12"/>
-      <c r="T38" s="16"/>
-      <c r="U38" s="16"/>
-      <c r="V38" s="17">
+      <c r="R38" s="17"/>
+      <c r="S38" s="15"/>
+      <c r="T38" s="19">
+        <v>6854</v>
+      </c>
+      <c r="U38" s="20"/>
+      <c r="V38" s="21">
         <v>46218</v>
       </c>
-      <c r="W38" s="25">
+      <c r="W38" s="29">
         <v>0.126470499289322</v>
       </c>
-      <c r="X38" s="16">
+      <c r="X38" s="20">
         <v>0.243112468624308</v>
       </c>
-      <c r="Y38" s="26">
+      <c r="Y38" s="30">
         <v>0.63041703208637</v>
       </c>
-      <c r="Z38" s="16">
+      <c r="Z38" s="20">
         <v>0.262880168857335</v>
       </c>
-      <c r="AA38" s="16">
+      <c r="AA38" s="20">
         <v>0.240381847836515</v>
       </c>
-      <c r="AB38" s="27">
+      <c r="AB38" s="31">
         <v>0.49673798330615</v>
       </c>
-      <c r="AC38" s="14">
+      <c r="AC38" s="17">
         <v>20846</v>
       </c>
-      <c r="AD38" s="22"/>
+      <c r="AD38" s="26"/>
     </row>
     <row r="39" spans="1:30">
-      <c r="A39" s="23">
+      <c r="A39" s="27">
         <v>32390</v>
       </c>
-      <c r="B39" s="11">
+      <c r="B39" s="14">
         <v>637</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="15">
         <v>0.0196665637542451</v>
       </c>
-      <c r="D39" s="13">
+      <c r="D39" s="16">
         <v>31</v>
       </c>
-      <c r="E39" s="12">
+      <c r="E39" s="15">
         <v>0.000957085520222291</v>
       </c>
-      <c r="F39" s="13">
+      <c r="F39" s="16">
         <v>7700</v>
       </c>
-      <c r="G39" s="12">
+      <c r="G39" s="15">
         <v>0.237727693732634</v>
       </c>
-      <c r="H39" s="13">
+      <c r="H39" s="16">
         <v>337</v>
       </c>
-      <c r="I39" s="12">
+      <c r="I39" s="15">
         <v>0.0104044458166101</v>
       </c>
-      <c r="J39" s="14">
+      <c r="J39" s="17">
         <v>5335</v>
       </c>
-      <c r="K39" s="12">
+      <c r="K39" s="15">
         <v>0.16471133065761</v>
       </c>
-      <c r="L39" s="13">
+      <c r="L39" s="16">
         <v>5016</v>
       </c>
-      <c r="M39" s="12">
+      <c r="M39" s="15">
         <v>0.154862611917258</v>
       </c>
-      <c r="N39" s="13">
+      <c r="N39" s="16">
         <v>9862</v>
       </c>
-      <c r="O39" s="12">
+      <c r="O39" s="15">
         <v>0.304476690336524</v>
       </c>
-      <c r="P39" s="15">
+      <c r="P39" s="18">
         <v>400</v>
       </c>
-      <c r="Q39" s="12">
+      <c r="Q39" s="15">
         <v>0.0123494905835134</v>
       </c>
-      <c r="R39" s="14">
+      <c r="R39" s="17">
         <v>3072</v>
       </c>
-      <c r="S39" s="12">
+      <c r="S39" s="15">
         <v>0.0948440876813831</v>
       </c>
-      <c r="T39" s="16"/>
-      <c r="U39" s="16"/>
-      <c r="V39" s="17">
+      <c r="T39" s="19">
+        <v>6556</v>
+      </c>
+      <c r="U39" s="20"/>
+      <c r="V39" s="21">
         <v>46235</v>
       </c>
-      <c r="W39" s="25">
+      <c r="W39" s="29">
         <v>0.0206236492744674</v>
       </c>
-      <c r="X39" s="16">
+      <c r="X39" s="20">
         <v>0.342976227230627</v>
       </c>
-      <c r="Y39" s="26">
+      <c r="Y39" s="30">
         <v>0.636400123494906</v>
       </c>
-      <c r="Z39" s="16">
+      <c r="Z39" s="20">
         <v>0.258817251249212</v>
       </c>
-      <c r="AA39" s="16">
+      <c r="AA39" s="20">
         <v>0.24334158055596</v>
       </c>
-      <c r="AB39" s="27">
+      <c r="AB39" s="31">
         <v>0.497841168194828</v>
       </c>
-      <c r="AC39" s="14">
+      <c r="AC39" s="17">
         <v>20613</v>
       </c>
-      <c r="AD39" s="22"/>
+      <c r="AD39" s="26"/>
     </row>
     <row r="40" spans="1:30">
-      <c r="A40" s="23">
+      <c r="A40" s="27">
         <v>37558</v>
       </c>
-      <c r="B40" s="11">
+      <c r="B40" s="14">
         <v>1306</v>
       </c>
-      <c r="C40" s="12">
+      <c r="C40" s="15">
         <v>0.034772884605144</v>
       </c>
-      <c r="D40" s="13">
+      <c r="D40" s="16">
         <v>6000</v>
       </c>
-      <c r="E40" s="12">
+      <c r="E40" s="15">
         <v>0.159752915490708</v>
       </c>
-      <c r="F40" s="13">
+      <c r="F40" s="16">
         <v>3000</v>
       </c>
-      <c r="G40" s="12">
+      <c r="G40" s="15">
         <v>0.0798764577453538</v>
       </c>
-      <c r="H40" s="13">
+      <c r="H40" s="16">
         <v>337</v>
       </c>
-      <c r="I40" s="12">
+      <c r="I40" s="15">
         <v>0.00897278875339475</v>
       </c>
-      <c r="J40" s="14">
+      <c r="J40" s="17">
         <v>11096</v>
       </c>
-      <c r="K40" s="12">
+      <c r="K40" s="15">
         <v>0.295436391714149</v>
       </c>
-      <c r="L40" s="13">
+      <c r="L40" s="16">
         <v>5021</v>
       </c>
-      <c r="M40" s="12">
+      <c r="M40" s="15">
         <v>0.133686564779807</v>
       </c>
-      <c r="N40" s="13">
+      <c r="N40" s="16">
         <v>7326</v>
       </c>
-      <c r="O40" s="12">
+      <c r="O40" s="15">
         <v>0.195058309814154</v>
       </c>
-      <c r="P40" s="15">
+      <c r="P40" s="18">
         <v>400</v>
       </c>
-      <c r="Q40" s="12">
+      <c r="Q40" s="15">
         <v>0.0106501943660472</v>
       </c>
-      <c r="R40" s="14">
+      <c r="R40" s="17">
         <v>3072</v>
       </c>
-      <c r="S40" s="12">
+      <c r="S40" s="15">
         <v>0.0817934927312423</v>
       </c>
-      <c r="T40" s="16"/>
-      <c r="U40" s="16"/>
-      <c r="V40" s="17">
+      <c r="T40" s="19">
+        <v>6556</v>
+      </c>
+      <c r="U40" s="20"/>
+      <c r="V40" s="21">
         <v>46249</v>
       </c>
-      <c r="W40" s="25">
+      <c r="W40" s="29">
         <v>0.194525800095852</v>
       </c>
-      <c r="X40" s="16">
+      <c r="X40" s="20">
         <v>0.170642739229991</v>
       </c>
-      <c r="Y40" s="26">
+      <c r="Y40" s="30">
         <v>0.634831460674157</v>
       </c>
-      <c r="Z40" s="16">
+      <c r="Z40" s="20">
         <v>0.465377678983349</v>
       </c>
-      <c r="AA40" s="16">
+      <c r="AA40" s="20">
         <v>0.21058591620182</v>
       </c>
-      <c r="AB40" s="27">
+      <c r="AB40" s="31">
         <v>0.32403640481483</v>
       </c>
-      <c r="AC40" s="14">
+      <c r="AC40" s="17">
         <v>23843</v>
       </c>
-      <c r="AD40" s="22"/>
+      <c r="AD40" s="26"/>
     </row>
     <row r="41" spans="1:30">
-      <c r="A41" s="23">
+      <c r="A41" s="27">
         <v>38636</v>
       </c>
-      <c r="B41" s="11">
+      <c r="B41" s="14">
         <v>1204</v>
       </c>
-      <c r="C41" s="12">
+      <c r="C41" s="15">
         <v>0.0311626462366705</v>
       </c>
-      <c r="D41" s="13">
+      <c r="D41" s="16">
         <v>4003</v>
       </c>
-      <c r="E41" s="12">
+      <c r="E41" s="15">
         <v>0.103608033957967</v>
       </c>
-      <c r="F41" s="13">
+      <c r="F41" s="16">
         <v>3000</v>
       </c>
-      <c r="G41" s="12">
+      <c r="G41" s="15">
         <v>0.0776477896262553</v>
       </c>
-      <c r="H41" s="13">
+      <c r="H41" s="16">
         <v>336</v>
       </c>
-      <c r="I41" s="12">
+      <c r="I41" s="15">
         <v>0.00869655243814059</v>
       </c>
-      <c r="J41" s="14">
+      <c r="J41" s="17">
         <v>11412</v>
       </c>
-      <c r="K41" s="12">
+      <c r="K41" s="15">
         <v>0.295372191738275</v>
       </c>
-      <c r="L41" s="13">
+      <c r="L41" s="16">
         <v>5026</v>
       </c>
-      <c r="M41" s="12">
+      <c r="M41" s="15">
         <v>0.13008593022052</v>
       </c>
-      <c r="N41" s="13">
+      <c r="N41" s="16">
         <v>7111</v>
       </c>
-      <c r="O41" s="12">
+      <c r="O41" s="15">
         <v>0.184051144010767</v>
       </c>
-      <c r="P41" s="15">
+      <c r="P41" s="18">
         <v>400</v>
       </c>
-      <c r="Q41" s="12">
+      <c r="Q41" s="15">
         <v>0.010353038616834</v>
       </c>
-      <c r="R41" s="14">
+      <c r="R41" s="17">
         <v>6144</v>
       </c>
-      <c r="S41" s="12">
+      <c r="S41" s="15">
         <v>0.159022673154571</v>
       </c>
-      <c r="T41" s="16"/>
-      <c r="U41" s="16"/>
-      <c r="V41" s="17">
+      <c r="T41" s="19">
+        <v>6258</v>
+      </c>
+      <c r="U41" s="20"/>
+      <c r="V41" s="21">
         <v>46266</v>
       </c>
-      <c r="W41" s="25">
+      <c r="W41" s="29">
         <v>0.134770680194637</v>
       </c>
-      <c r="X41" s="16">
+      <c r="X41" s="20">
         <v>0.245367015218967</v>
       </c>
-      <c r="Y41" s="26">
+      <c r="Y41" s="30">
         <v>0.619862304586396</v>
       </c>
-      <c r="Z41" s="16">
+      <c r="Z41" s="20">
         <v>0.476512589252161</v>
       </c>
-      <c r="AA41" s="16">
+      <c r="AA41" s="20">
         <v>0.209862624744248</v>
       </c>
-      <c r="AB41" s="27">
+      <c r="AB41" s="31">
         <v>0.313624786003591</v>
       </c>
-      <c r="AC41" s="14">
+      <c r="AC41" s="17">
         <v>23949</v>
       </c>
-      <c r="AD41" s="22"/>
+      <c r="AD41" s="26"/>
     </row>
     <row r="42" spans="1:30">
-      <c r="A42" s="23">
+      <c r="A42" s="27">
         <v>37185</v>
       </c>
-      <c r="B42" s="11">
+      <c r="B42" s="14">
         <v>2936</v>
       </c>
-      <c r="C42" s="12">
+      <c r="C42" s="15">
         <v>0.0789565685088073</v>
       </c>
-      <c r="D42" s="13">
-        <v>0</v>
-      </c>
-      <c r="E42" s="12">
-        <v>0</v>
-      </c>
-      <c r="F42" s="13">
+      <c r="D42" s="16">
+        <v>0</v>
+      </c>
+      <c r="E42" s="15">
+        <v>0</v>
+      </c>
+      <c r="F42" s="16">
         <v>1000</v>
       </c>
-      <c r="G42" s="12">
+      <c r="G42" s="15">
         <v>0.026892564205997</v>
       </c>
-      <c r="H42" s="13">
+      <c r="H42" s="16">
         <v>335</v>
       </c>
-      <c r="I42" s="12">
+      <c r="I42" s="15">
         <v>0.00900900900900901</v>
       </c>
-      <c r="J42" s="14">
+      <c r="J42" s="17">
         <v>10500</v>
       </c>
-      <c r="K42" s="12">
+      <c r="K42" s="15">
         <v>0.282371924162969</v>
       </c>
-      <c r="L42" s="13">
+      <c r="L42" s="16">
         <v>7023</v>
       </c>
-      <c r="M42" s="12">
+      <c r="M42" s="15">
         <v>0.188866478418717</v>
       </c>
-      <c r="N42" s="13">
+      <c r="N42" s="16">
         <v>7847</v>
       </c>
-      <c r="O42" s="12">
+      <c r="O42" s="15">
         <v>0.211025951324459</v>
       </c>
-      <c r="P42" s="15">
+      <c r="P42" s="18">
         <v>1400</v>
       </c>
-      <c r="Q42" s="12">
+      <c r="Q42" s="15">
         <v>0.0376495898883959</v>
       </c>
-      <c r="R42" s="14">
+      <c r="R42" s="17">
         <v>6144</v>
       </c>
-      <c r="S42" s="12">
+      <c r="S42" s="15">
         <v>0.165227914481646</v>
       </c>
-      <c r="T42" s="16"/>
-      <c r="U42" s="16"/>
-      <c r="V42" s="17">
+      <c r="T42" s="19">
+        <v>6258</v>
+      </c>
+      <c r="U42" s="20"/>
+      <c r="V42" s="21">
         <v>46280</v>
       </c>
-      <c r="W42" s="25">
+      <c r="W42" s="29">
         <v>0.0789565685088073</v>
       </c>
-      <c r="X42" s="16">
+      <c r="X42" s="20">
         <v>0.201129487696652</v>
       </c>
-      <c r="Y42" s="26">
+      <c r="Y42" s="30">
         <v>0.719913943794541</v>
       </c>
-      <c r="Z42" s="16">
+      <c r="Z42" s="20">
         <v>0.39223010833022</v>
       </c>
-      <c r="AA42" s="16">
+      <c r="AA42" s="20">
         <v>0.262345909600299</v>
       </c>
-      <c r="AB42" s="27">
+      <c r="AB42" s="31">
         <v>0.345423982069481</v>
       </c>
-      <c r="AC42" s="14">
+      <c r="AC42" s="17">
         <v>26770</v>
       </c>
-      <c r="AD42" s="22"/>
+      <c r="AD42" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\work\Work\Project\financial_management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C53A5F-E745-4339-ADE4-8214770546EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B489823-952A-47C3-A6E8-CC6CEF1CA283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -453,19 +453,31 @@
     <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -481,18 +493,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -799,104 +799,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="42"/>
       <c r="J1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="45" t="s">
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="45"/>
+      <c r="S1" s="49"/>
       <c r="T1" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="47"/>
-      <c r="V1" s="48" t="s">
+      <c r="U1" s="43"/>
+      <c r="V1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="37" t="s">
+      <c r="W1" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="38"/>
-      <c r="Z1" s="38"/>
-      <c r="AA1" s="38"/>
-      <c r="AB1" s="38"/>
-      <c r="AC1" s="38"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
+      <c r="AB1" s="45"/>
+      <c r="AC1" s="45"/>
       <c r="AD1" s="10"/>
     </row>
     <row r="2" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="39"/>
-      <c r="B2" s="39" t="s">
+      <c r="A2" s="37"/>
+      <c r="B2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="39"/>
+      <c r="C2" s="37"/>
       <c r="D2" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="39" t="s">
+      <c r="E2" s="42"/>
+      <c r="F2" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="39"/>
+      <c r="G2" s="37"/>
       <c r="H2" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="41"/>
+      <c r="I2" s="42"/>
       <c r="J2" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="41"/>
-      <c r="L2" s="39" t="s">
+      <c r="K2" s="42"/>
+      <c r="L2" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39" t="s">
+      <c r="M2" s="37"/>
+      <c r="N2" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39" t="s">
+      <c r="O2" s="37"/>
+      <c r="P2" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="46" t="s">
+      <c r="Q2" s="37"/>
+      <c r="R2" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="47"/>
+      <c r="S2" s="43"/>
       <c r="T2" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="47"/>
-      <c r="V2" s="49"/>
-      <c r="W2" s="42" t="s">
+      <c r="U2" s="43"/>
+      <c r="V2" s="39"/>
+      <c r="W2" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="44"/>
-      <c r="Z2" s="42" t="s">
+      <c r="X2" s="47"/>
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="AA2" s="43"/>
-      <c r="AB2" s="44"/>
+      <c r="AA2" s="47"/>
+      <c r="AB2" s="48"/>
       <c r="AC2" s="11" t="s">
         <v>15</v>
       </c>
@@ -3506,56 +3506,56 @@
         <v>2294</v>
       </c>
       <c r="C39" s="15">
-        <f t="shared" ref="C39:C45" si="66">B39/A39</f>
+        <f t="shared" ref="C39:C46" si="66">B39/A39</f>
         <v>6.160042964554243E-2</v>
       </c>
       <c r="D39" s="23">
         <v>1556</v>
       </c>
       <c r="E39" s="15">
-        <f t="shared" ref="E39:E45" si="67">D39/A39</f>
+        <f t="shared" ref="E39:E46" si="67">D39/A39</f>
         <v>4.1783029001074112E-2</v>
       </c>
       <c r="F39" s="23">
         <v>7700</v>
       </c>
       <c r="G39" s="15">
-        <f t="shared" ref="G39:G45" si="68">F39/A39</f>
+        <f t="shared" ref="G39:G46" si="68">F39/A39</f>
         <v>0.20676691729323307</v>
       </c>
       <c r="H39" s="24">
         <v>5194</v>
       </c>
       <c r="I39" s="15">
-        <f t="shared" ref="I39:I45" si="69">H39/A39</f>
+        <f t="shared" ref="I39:I46" si="69">H39/A39</f>
         <v>0.13947368421052631</v>
       </c>
       <c r="J39" s="25">
         <v>6525</v>
       </c>
       <c r="K39" s="15">
-        <f t="shared" ref="K39:K45" si="70">J39/A39</f>
+        <f t="shared" ref="K39:K46" si="70">J39/A39</f>
         <v>0.17521482277121375</v>
       </c>
       <c r="L39" s="23">
         <v>5000</v>
       </c>
       <c r="M39" s="15">
-        <f t="shared" ref="M39:M45" si="71">L39/A39</f>
+        <f t="shared" ref="M39:M46" si="71">L39/A39</f>
         <v>0.13426423200859292</v>
       </c>
       <c r="N39" s="23">
         <v>8571</v>
       </c>
       <c r="O39" s="15">
-        <f t="shared" ref="O39:O45" si="72">N39/A39</f>
+        <f t="shared" ref="O39:O46" si="72">N39/A39</f>
         <v>0.23015574650912995</v>
       </c>
       <c r="P39" s="26">
         <v>400</v>
       </c>
       <c r="Q39" s="15">
-        <f t="shared" ref="Q39:Q45" si="73">P39/A39</f>
+        <f t="shared" ref="Q39:Q46" si="73">P39/A39</f>
         <v>1.0741138560687433E-2</v>
       </c>
       <c r="R39" s="18"/>
@@ -4211,28 +4211,108 @@
       </c>
     </row>
     <row r="46" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="32"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="33"/>
-      <c r="D46" s="23"/>
-      <c r="E46" s="33"/>
-      <c r="F46" s="23"/>
-      <c r="G46" s="33"/>
-      <c r="H46" s="24"/>
-      <c r="I46" s="33"/>
-      <c r="J46" s="25"/>
-      <c r="K46" s="33"/>
-      <c r="L46" s="23"/>
-      <c r="M46" s="33"/>
-      <c r="N46" s="16"/>
-      <c r="O46" s="33"/>
-      <c r="P46" s="26"/>
-      <c r="Q46" s="33"/>
-      <c r="R46" s="25"/>
-      <c r="S46" s="33"/>
-      <c r="T46" s="25"/>
+      <c r="A46" s="21">
+        <f>SUM(B46,D46,F46,H46,J46,L46,N46,P46,R46)</f>
+        <v>37077</v>
+      </c>
+      <c r="B46" s="22">
+        <v>2349</v>
+      </c>
+      <c r="C46" s="15">
+        <f t="shared" si="66"/>
+        <v>6.3354640343069826E-2</v>
+      </c>
+      <c r="D46" s="23">
+        <v>0</v>
+      </c>
+      <c r="E46" s="15">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="F46" s="23">
+        <v>1000</v>
+      </c>
+      <c r="G46" s="15">
+        <f t="shared" si="68"/>
+        <v>2.6970898400625724E-2</v>
+      </c>
+      <c r="H46" s="24">
+        <v>335</v>
+      </c>
+      <c r="I46" s="15">
+        <f t="shared" si="69"/>
+        <v>9.0352509642096183E-3</v>
+      </c>
+      <c r="J46" s="25">
+        <v>6697</v>
+      </c>
+      <c r="K46" s="15">
+        <f t="shared" si="70"/>
+        <v>0.18062410658899047</v>
+      </c>
+      <c r="L46" s="23">
+        <v>12040</v>
+      </c>
+      <c r="M46" s="15">
+        <f t="shared" si="71"/>
+        <v>0.32472961674353373</v>
+      </c>
+      <c r="N46" s="16">
+        <v>7110</v>
+      </c>
+      <c r="O46" s="15">
+        <f t="shared" si="72"/>
+        <v>0.1917630876284489</v>
+      </c>
+      <c r="P46" s="26">
+        <v>1402</v>
+      </c>
+      <c r="Q46" s="15">
+        <f t="shared" si="73"/>
+        <v>3.7813199557677264E-2</v>
+      </c>
+      <c r="R46" s="25">
+        <v>6144</v>
+      </c>
+      <c r="S46" s="15">
+        <f>R46/A46</f>
+        <v>0.16570919977344445</v>
+      </c>
+      <c r="T46" s="25">
+        <v>5970</v>
+      </c>
       <c r="U46" s="33"/>
-      <c r="V46" s="23"/>
+      <c r="V46" s="27">
+        <v>46296</v>
+      </c>
+      <c r="W46" s="28">
+        <f t="shared" ref="W46" si="86">(B46+D46)/A46</f>
+        <v>6.3354640343069826E-2</v>
+      </c>
+      <c r="X46" s="29">
+        <f>(F46+H46+R46)/A46</f>
+        <v>0.20171534913827979</v>
+      </c>
+      <c r="Y46" s="30">
+        <f t="shared" ref="Y46" si="87">(J46+L46+N46+P46)/A46</f>
+        <v>0.73493001051865037</v>
+      </c>
+      <c r="Z46" s="29">
+        <f t="shared" ref="Z46" si="88">J46/(J46+L46+N46+P46)</f>
+        <v>0.24577048699034826</v>
+      </c>
+      <c r="AA46" s="29">
+        <f t="shared" ref="AA46" si="89">(L46)/(J46+L46+N46+P46)</f>
+        <v>0.44185107710374694</v>
+      </c>
+      <c r="AB46" s="31">
+        <f t="shared" ref="AB46" si="90">(N46+P46)/(J46+L46+N46+P46)</f>
+        <v>0.31237843590590481</v>
+      </c>
+      <c r="AC46" s="25">
+        <f t="shared" ref="AC46" si="91">J46+L46+N46+P46</f>
+        <v>27249</v>
+      </c>
     </row>
     <row r="47" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="32"/>
@@ -6492,12 +6572,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="V1:V2"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="J1:Q1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T2:U2"/>
     <mergeCell ref="W1:AC1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
@@ -6511,6 +6585,12 @@
     <mergeCell ref="Z2:AB2"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="R2:S2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="V1:V2"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T2:U2"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
